--- a/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Mission Profiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A2CC4B-A671-4605-8AA5-F5356594AEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468D43F9-C252-4E3A-9570-E738789EECA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3408" yWindow="324" windowWidth="18684" windowHeight="10992" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
-    <sheet name="JetSubmersible" sheetId="13" r:id="rId2"/>
-    <sheet name="Electric C172" sheetId="6" r:id="rId3"/>
+    <sheet name="JetSubmersible" sheetId="14" r:id="rId2"/>
+    <sheet name="JetSubmersible2" sheetId="13" r:id="rId3"/>
+    <sheet name="Electric C172" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="39">
   <si>
     <t>Takeoff</t>
   </si>
@@ -405,7 +406,492 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -869,19 +1355,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{76C479A7-D97E-3440-915F-4416140AAFD6}" name="Table3235" displayName="Table3235" ref="A1:J200" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5873046A-D94B-4CE6-B113-0C195A1942AA}" name="Table32352" displayName="Table32352" ref="A1:J200" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20">
   <autoFilter ref="A1:J200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{15EB4EF6-08A8-964E-ABD5-0CF3EEC0C7B7}" name="Segment #" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{10C18371-46B8-6544-9972-D21BFA1DB0CD}" name="Segment Type" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{526667C5-306E-7D43-B338-699328AA6680}" name="Input 1" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{285F1D9C-6790-F049-8810-78F8A349CEA8}" name="Input 2" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{414CB0C1-F49D-4248-9E2F-428FEB38D5DA}" name="Input 3" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{7993028E-EBAF-D840-BAB7-8BA72340BA98}" name="Input 4" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{6617A981-14C9-8C42-A72A-0EB397E2F530}" name="Input 5" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{7AE9ECDF-5690-DE42-BC09-5934349F52E2}" name="Input 6" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{D1E2BD85-064E-C746-9E9E-6DA887B3E2CA}" name="Input 7" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{F7213638-D701-E04E-A444-9564EC9CA3EE}" name="Input 8" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{29582358-02F8-42CF-976E-B4263AB788DB}" name="Segment #" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{6C13E2E5-4373-40A5-8BA7-87D226CC2263}" name="Segment Type" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{7A448FD4-A393-4071-98A4-7E1C0373E44C}" name="Input 1" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{796A18A1-D6B7-4094-8522-B615C2B359E4}" name="Input 2" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{CE5DD5A2-CB44-46A9-82A3-19FC49260471}" name="Input 3" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{816496A7-4FB6-4095-963C-AAE3CE031309}" name="Input 4" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{836D47FC-8E1A-4872-9384-56541ED32AD7}" name="Input 5" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{B175F230-C0EB-4A2F-9252-7210267D9B0F}" name="Input 6" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{E72F55D3-1483-44B0-BCF0-8F74A034E54D}" name="Input 7" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{AA8DF749-4D5E-436D-BB46-0C1D1C6157E2}" name="Input 8" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{76C479A7-D97E-3440-915F-4416140AAFD6}" name="Table3235" displayName="Table3235" ref="A1:J200" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" tableBorderDxfId="51">
+  <autoFilter ref="A1:J200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{15EB4EF6-08A8-964E-ABD5-0CF3EEC0C7B7}" name="Segment #" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{10C18371-46B8-6544-9972-D21BFA1DB0CD}" name="Segment Type" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{526667C5-306E-7D43-B338-699328AA6680}" name="Input 1" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{285F1D9C-6790-F049-8810-78F8A349CEA8}" name="Input 2" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{414CB0C1-F49D-4248-9E2F-428FEB38D5DA}" name="Input 3" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{7993028E-EBAF-D840-BAB7-8BA72340BA98}" name="Input 4" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{6617A981-14C9-8C42-A72A-0EB397E2F530}" name="Input 5" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{7AE9ECDF-5690-DE42-BC09-5934349F52E2}" name="Input 6" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{D1E2BD85-064E-C746-9E9E-6DA887B3E2CA}" name="Input 7" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{F7213638-D701-E04E-A444-9564EC9CA3EE}" name="Input 8" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1535,12 +2040,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A25:E26">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:F12 F13:F20 B15:E20 A21:F21 B22:F23">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1549,6 +2054,2816 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ACEB7F5-011B-4BE7-B66A-4C84EF6B50B4}">
+  <dimension ref="A1:J200"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="10.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16.2" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.6">
+      <c r="A2" s="15">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6">
+      <c r="A3" s="8"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="20">
+        <v>0.995</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.6">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.6">
+      <c r="A5" s="8"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26">
+        <v>0</v>
+      </c>
+      <c r="D5" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E5" s="26">
+        <v>0.08</v>
+      </c>
+      <c r="F5" s="26">
+        <v>0</v>
+      </c>
+      <c r="G5" s="26"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.6">
+      <c r="A6" s="8">
+        <v>3</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.6">
+      <c r="A7" s="8"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.6">
+      <c r="A8" s="8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.6">
+      <c r="A9" s="8"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="21">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.6">
+      <c r="A10" s="8">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="21">
+        <v>15000</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="21">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.6">
+      <c r="A12" s="8">
+        <v>6</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.6">
+      <c r="A13" s="8"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21">
+        <v>15000</v>
+      </c>
+      <c r="D13" s="21">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="F13" s="21">
+        <v>0.49</v>
+      </c>
+      <c r="G13" s="21">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.6">
+      <c r="A14" s="8">
+        <v>7</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="23"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.6">
+      <c r="A15" s="8"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26">
+        <v>20000</v>
+      </c>
+      <c r="D15" s="26">
+        <v>200</v>
+      </c>
+      <c r="E15" s="26">
+        <v>0.49</v>
+      </c>
+      <c r="F15" s="26">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.6">
+      <c r="A16" s="8">
+        <v>8</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.6">
+      <c r="A17" s="8"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="3">
+        <v>20000</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.6">
+      <c r="A18" s="8">
+        <v>9</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.6">
+      <c r="A19" s="8"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="26">
+        <v>0.99</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.6">
+      <c r="A20" s="8">
+        <v>10</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.6">
+      <c r="A21" s="6"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="20">
+        <v>0.999</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.6">
+      <c r="A22" s="6">
+        <v>11</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="23"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.6">
+      <c r="A23" s="6"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="26">
+        <v>0</v>
+      </c>
+      <c r="D23" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E23" s="26">
+        <v>0.08</v>
+      </c>
+      <c r="F23" s="26">
+        <v>0</v>
+      </c>
+      <c r="G23" s="26"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.6">
+      <c r="A24" s="6">
+        <v>12</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="6"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21">
+        <v>0</v>
+      </c>
+      <c r="D25" s="21">
+        <v>5000</v>
+      </c>
+      <c r="E25" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="F25" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.6">
+      <c r="A26" s="6">
+        <v>13</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="6"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21">
+        <v>5000</v>
+      </c>
+      <c r="D27" s="21">
+        <v>10000</v>
+      </c>
+      <c r="E27" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="F27" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="21">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.6">
+      <c r="A28" s="6">
+        <v>14</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="6"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21">
+        <v>10000</v>
+      </c>
+      <c r="D29" s="21">
+        <v>15000</v>
+      </c>
+      <c r="E29" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="F29" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="21">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.6">
+      <c r="A30" s="6">
+        <v>15</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="6"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21">
+        <v>15000</v>
+      </c>
+      <c r="D31" s="21">
+        <v>20000</v>
+      </c>
+      <c r="E31" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="F31" s="21">
+        <v>0.49</v>
+      </c>
+      <c r="G31" s="21">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.6">
+      <c r="A32" s="6">
+        <v>16</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="23"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="9"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.6">
+      <c r="A33" s="6"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26">
+        <v>10000</v>
+      </c>
+      <c r="D33" s="26">
+        <v>25</v>
+      </c>
+      <c r="E33" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="F33" s="26">
+        <v>0</v>
+      </c>
+      <c r="G33" s="26"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="9"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.6">
+      <c r="A34" s="6">
+        <v>17</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="9"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.6">
+      <c r="A35" s="6"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="9"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.6">
+      <c r="A36" s="6">
+        <v>18</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="9"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.6">
+      <c r="A37" s="6"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26">
+        <v>0.99</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="9"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.6">
+      <c r="A38" s="6">
+        <v>19</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="9"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.6">
+      <c r="A39" s="6"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="20">
+        <v>0.999</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="9"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="6"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="9"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="6"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="9"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="6"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="9"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="6"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="9"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="6"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="9"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="6"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="9"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="6"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="9"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="6"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="9"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="6"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="9"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="6"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="9"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="6"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="9"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="6"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="9"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="6"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="9"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="6"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="9"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="6"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="9"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="6"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="9"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="6"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="9"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="6"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="9"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="6"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="9"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="6"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="9"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="6"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="9"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="6"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="9"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="6"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="9"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="6"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="9"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="6"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="9"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="6"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="9"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="6"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="9"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="6"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="9"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="6"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="9"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="6"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="9"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="6"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="9"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="6"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="9"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="6"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="9"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="6"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="9"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="6"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="9"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="6"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="9"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="6"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="9"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="6"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="9"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="6"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="9"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="6"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="9"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="6"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="9"/>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="6"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="9"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="6"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="9"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="6"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="9"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="6"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="9"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="6"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="9"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="6"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="9"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="6"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="9"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="6"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="9"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="6"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="9"/>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="6"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="9"/>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="6"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="9"/>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="6"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="9"/>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="6"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="9"/>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="6"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="9"/>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="6"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="9"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="6"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="9"/>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="6"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="9"/>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="6"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="9"/>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="6"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="9"/>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="6"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="9"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="6"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="9"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="6"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="9"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="6"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="9"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="6"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="9"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="6"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="9"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="6"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="9"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="6"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="9"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="6"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="9"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="6"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="9"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="6"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="9"/>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="6"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="9"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="6"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="9"/>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="6"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="9"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="6"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="9"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="6"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="9"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" s="6"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="9"/>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="6"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="9"/>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="6"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="9"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="6"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="9"/>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" s="6"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="9"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" s="6"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="9"/>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" s="6"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="9"/>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" s="6"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="9"/>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" s="6"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="9"/>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" s="6"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="9"/>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" s="6"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="9"/>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" s="6"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="9"/>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" s="6"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="9"/>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="6"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="9"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="6"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="9"/>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" s="6"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="9"/>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="6"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="9"/>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="6"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="9"/>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" s="6"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="9"/>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" s="6"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="9"/>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" s="6"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="9"/>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" s="6"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="9"/>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" s="6"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="9"/>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" s="6"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="9"/>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" s="6"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="9"/>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" s="6"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="9"/>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" s="6"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="9"/>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" s="6"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="9"/>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" s="6"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="9"/>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" s="6"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="9"/>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" s="6"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="9"/>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" s="6"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="9"/>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" s="6"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="9"/>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" s="6"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="9"/>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" s="6"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="9"/>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" s="6"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="9"/>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152" s="6"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="9"/>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153" s="6"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="9"/>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154" s="6"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="9"/>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" s="6"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="3"/>
+      <c r="J155" s="9"/>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156" s="6"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="9"/>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157" s="6"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="9"/>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" s="6"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="9"/>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159" s="6"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+      <c r="J159" s="9"/>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160" s="6"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="3"/>
+      <c r="J160" s="9"/>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" s="6"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3"/>
+      <c r="J161" s="9"/>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" s="6"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="3"/>
+      <c r="J162" s="9"/>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" s="6"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="3"/>
+      <c r="J163" s="9"/>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" s="6"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+      <c r="J164" s="9"/>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165" s="6"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+      <c r="J165" s="9"/>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166" s="6"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="9"/>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167" s="6"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="3"/>
+      <c r="J167" s="9"/>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168" s="6"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="3"/>
+      <c r="J168" s="9"/>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169" s="6"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="3"/>
+      <c r="J169" s="9"/>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170" s="6"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+      <c r="I170" s="3"/>
+      <c r="J170" s="9"/>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171" s="6"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+      <c r="I171" s="3"/>
+      <c r="J171" s="9"/>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172" s="6"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="3"/>
+      <c r="J172" s="9"/>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173" s="6"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3"/>
+      <c r="J173" s="9"/>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174" s="6"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+      <c r="J174" s="9"/>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175" s="6"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+      <c r="J175" s="9"/>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176" s="6"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="3"/>
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+      <c r="I176" s="3"/>
+      <c r="J176" s="9"/>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177" s="6"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="3"/>
+      <c r="H177" s="3"/>
+      <c r="I177" s="3"/>
+      <c r="J177" s="9"/>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178" s="6"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3"/>
+      <c r="H178" s="3"/>
+      <c r="I178" s="3"/>
+      <c r="J178" s="9"/>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179" s="6"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+      <c r="I179" s="3"/>
+      <c r="J179" s="9"/>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180" s="6"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+      <c r="I180" s="3"/>
+      <c r="J180" s="9"/>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" s="6"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3"/>
+      <c r="J181" s="9"/>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" s="6"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+      <c r="J182" s="9"/>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183" s="6"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+      <c r="J183" s="9"/>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184" s="6"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="J184" s="9"/>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" s="6"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
+      <c r="I185" s="3"/>
+      <c r="J185" s="9"/>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" s="6"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="3"/>
+      <c r="G186" s="3"/>
+      <c r="H186" s="3"/>
+      <c r="I186" s="3"/>
+      <c r="J186" s="9"/>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187" s="6"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="3"/>
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+      <c r="I187" s="3"/>
+      <c r="J187" s="9"/>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188" s="6"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="3"/>
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+      <c r="I188" s="3"/>
+      <c r="J188" s="9"/>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189" s="6"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="3"/>
+      <c r="F189" s="3"/>
+      <c r="G189" s="3"/>
+      <c r="H189" s="3"/>
+      <c r="I189" s="3"/>
+      <c r="J189" s="9"/>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190" s="6"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="3"/>
+      <c r="F190" s="3"/>
+      <c r="G190" s="3"/>
+      <c r="H190" s="3"/>
+      <c r="I190" s="3"/>
+      <c r="J190" s="9"/>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191" s="6"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+      <c r="I191" s="3"/>
+      <c r="J191" s="9"/>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192" s="6"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+      <c r="J192" s="9"/>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" s="6"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="3"/>
+      <c r="F193" s="3"/>
+      <c r="G193" s="3"/>
+      <c r="H193" s="3"/>
+      <c r="I193" s="3"/>
+      <c r="J193" s="9"/>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" s="6"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
+      <c r="F194" s="3"/>
+      <c r="G194" s="3"/>
+      <c r="H194" s="3"/>
+      <c r="I194" s="3"/>
+      <c r="J194" s="9"/>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195" s="6"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="3"/>
+      <c r="F195" s="3"/>
+      <c r="G195" s="3"/>
+      <c r="H195" s="3"/>
+      <c r="I195" s="3"/>
+      <c r="J195" s="9"/>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196" s="6"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="3"/>
+      <c r="F196" s="3"/>
+      <c r="G196" s="3"/>
+      <c r="H196" s="3"/>
+      <c r="I196" s="3"/>
+      <c r="J196" s="9"/>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197" s="6"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+      <c r="E197" s="3"/>
+      <c r="F197" s="3"/>
+      <c r="G197" s="3"/>
+      <c r="H197" s="3"/>
+      <c r="I197" s="3"/>
+      <c r="J197" s="9"/>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" s="6"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="3"/>
+      <c r="F198" s="3"/>
+      <c r="G198" s="3"/>
+      <c r="H198" s="3"/>
+      <c r="I198" s="3"/>
+      <c r="J198" s="9"/>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199" s="6"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
+      <c r="E199" s="3"/>
+      <c r="F199" s="3"/>
+      <c r="G199" s="3"/>
+      <c r="H199" s="3"/>
+      <c r="I199" s="3"/>
+      <c r="J199" s="9"/>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200" s="10"/>
+      <c r="B200" s="11"/>
+      <c r="C200" s="11"/>
+      <c r="D200" s="11"/>
+      <c r="E200" s="11"/>
+      <c r="F200" s="11"/>
+      <c r="G200" s="11"/>
+      <c r="H200" s="11"/>
+      <c r="I200" s="11"/>
+      <c r="J200" s="12"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A2 H2:XFD19">
+    <cfRule type="expression" dxfId="29" priority="9">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1 D1:J1">
+    <cfRule type="expression" dxfId="28" priority="10">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:XFD1 A40:XFD1048576 A22:A39 H20:XFD39">
+    <cfRule type="expression" dxfId="23" priority="11">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G15 C18:G33">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16:G17 G34:G35 C36:G39">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{695D9087-805A-4F5B-A8A5-53B137FE94CA}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -2180,13 +5495,13 @@
       <c r="F39" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A39:F39 B1:F14 B17:F32">
-    <cfRule type="expression" dxfId="8" priority="2">
+  <conditionalFormatting sqref="B1:F14 B17:F32 A39:F39">
+    <cfRule type="expression" dxfId="38" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F16 F33:F34 B35:F38">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2194,7 +5509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23008A42-2183-AF47-B42B-F6CD8E247DCD}">
   <dimension ref="A1:J200"/>
   <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15"/>
@@ -4770,37 +8085,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2 F2:XFD3 B2:E11 H4:XFD7 G8:XFD11 F12:XFD19">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="36" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="35" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:D13">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:E15">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F11">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="32" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G7">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="31" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:XFD1 E20:XFD21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="30" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="39">
   <si>
     <t xml:space="preserve">Startup/Taxi</t>
   </si>
@@ -531,8 +531,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table32352" displayName="Table32352" ref="A1:J210" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J210"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table32352" displayName="Table32352" ref="A1:J212" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J212"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Segment #"/>
     <tableColumn id="2" name="Segment Type"/>
@@ -908,7 +908,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1048576"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.8"/>
@@ -1027,7 +1027,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="11"/>
     </row>
-    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
@@ -1053,7 +1053,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="n">
@@ -1066,7 +1066,7 @@
         <v>0.1</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1075,7 +1075,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="11"/>
     </row>
-    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -1101,7 +1101,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="11"/>
     </row>
-    <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="n">
@@ -1111,10 +1111,10 @@
         <v>10000</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="n">
         <v>5</v>
       </c>
@@ -1149,7 +1149,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="n">
@@ -1159,10 +1159,10 @@
         <v>15000</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="11"/>
     </row>
-    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="n">
         <v>6</v>
       </c>
@@ -1207,10 +1207,10 @@
         <v>20000</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>25000</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -1303,10 +1303,10 @@
         <v>30000</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
@@ -1351,10 +1351,10 @@
         <v>35000</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>200</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0.1</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
@@ -1639,10 +1639,10 @@
         <v>10000</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
@@ -1687,10 +1687,10 @@
         <v>15000</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>20000</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>25000</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>30000</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0</v>
@@ -1879,10 +1879,10 @@
         <v>35000</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>0</v>
@@ -1896,37 +1896,41 @@
         <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
+      <c r="D44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E45" s="5" t="n">
+      <c r="B45" s="12"/>
+      <c r="C45" s="13" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="G45" s="13"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="11"/>
@@ -1936,29 +1940,37 @@
         <v>23</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="13" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="11"/>
@@ -1968,9 +1980,9 @@
         <v>24</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D48" s="3"/>
@@ -1983,26 +1995,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="4" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="A50" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="11"/>
@@ -2010,7 +2028,9 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
+      <c r="C51" s="4" t="n">
+        <v>0.999</v>
+      </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
@@ -2057,24 +2077,24 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14"/>
-      <c r="B55" s="0"/>
-      <c r="C55" s="0"/>
-      <c r="D55" s="0"/>
-      <c r="E55" s="0"/>
-      <c r="F55" s="0"/>
-      <c r="G55" s="0"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14"/>
-      <c r="B56" s="0"/>
-      <c r="C56" s="0"/>
-      <c r="D56" s="0"/>
-      <c r="E56" s="0"/>
-      <c r="F56" s="0"/>
-      <c r="G56" s="0"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="11"/>
@@ -2129,24 +2149,24 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="B61" s="0"/>
+      <c r="C61" s="0"/>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0"/>
+      <c r="G61" s="0"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="11"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
+      <c r="B62" s="0"/>
+      <c r="C62" s="0"/>
+      <c r="D62" s="0"/>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0"/>
+      <c r="G62" s="0"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="11"/>
@@ -3916,19 +3936,41 @@
       <c r="J209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="15"/>
-      <c r="B210" s="16"/>
-      <c r="C210" s="16"/>
-      <c r="D210" s="16"/>
-      <c r="E210" s="16"/>
-      <c r="F210" s="16"/>
-      <c r="G210" s="16"/>
-      <c r="H210" s="16"/>
-      <c r="I210" s="16"/>
-      <c r="J210" s="17"/>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A210" s="14"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="5"/>
+      <c r="D210" s="5"/>
+      <c r="E210" s="5"/>
+      <c r="F210" s="5"/>
+      <c r="G210" s="5"/>
+      <c r="H210" s="5"/>
+      <c r="I210" s="5"/>
+      <c r="J210" s="11"/>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="14"/>
+      <c r="B211" s="5"/>
+      <c r="C211" s="5"/>
+      <c r="D211" s="5"/>
+      <c r="E211" s="5"/>
+      <c r="F211" s="5"/>
+      <c r="G211" s="5"/>
+      <c r="H211" s="5"/>
+      <c r="I211" s="5"/>
+      <c r="J211" s="11"/>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="15"/>
+      <c r="B212" s="16"/>
+      <c r="C212" s="16"/>
+      <c r="D212" s="16"/>
+      <c r="E212" s="16"/>
+      <c r="F212" s="16"/>
+      <c r="G212" s="16"/>
+      <c r="H212" s="16"/>
+      <c r="I212" s="16"/>
+      <c r="J212" s="17"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2 H2:AMJ25">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
@@ -3940,17 +3982,17 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:AMJ1 A50:AMJ54 A44:A49 H26:AMJ49 A61:AMJ1048576 A55:A60 H55:AMJ60 A28:A43">
+  <conditionalFormatting sqref="K1:AMJ1 A52:AMJ56 H26:AMJ51 A63:AMJ1048576 A57:A62 H57:AMJ62 A28:A51">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G21 C24:G43">
+  <conditionalFormatting sqref="C24:G45 C2:G21">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G23 G44:G45 C46:G49">
+  <conditionalFormatting sqref="G22:G23 G46:G47 C48:G51">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Mission Profiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1357D336-DEF2-499A-829A-BE479EC4BE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9EE423-0FE6-41AF-A94F-2A67136B10F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="1" r:id="rId1"/>
     <sheet name="JetSubmersible" sheetId="2" r:id="rId2"/>
-    <sheet name="Electric C172" sheetId="4" r:id="rId3"/>
+    <sheet name="JetSubmersibleDrop" sheetId="5" r:id="rId3"/>
+    <sheet name="Electric C172" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="39">
   <si>
     <t>Startup/Taxi</t>
   </si>
@@ -381,7 +382,10 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="23">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
@@ -530,8 +534,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table32352" displayName="Table32352" ref="A1:J214" totalsRowShown="0">
-  <autoFilter ref="A1:J214" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table32352" displayName="Table32352" ref="A1:J212" totalsRowShown="0">
+  <autoFilter ref="A1:J212" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Segment #"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Segment Type"/>
@@ -549,6 +553,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AE63C51F-3251-414D-B554-0C05CDF493D6}" name="Table323524" displayName="Table323524" ref="A1:J214" totalsRowShown="0">
+  <autoFilter ref="A1:J214" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{4659FCE2-E25D-48AA-89F4-F0BBB5B587AC}" name="Segment #"/>
+    <tableColumn id="2" xr3:uid="{58B7FC18-0858-4DEA-ACC7-3666A9454C35}" name="Segment Type"/>
+    <tableColumn id="3" xr3:uid="{C3ECEC8F-EAC9-42CD-8DC6-92703EDAEDCB}" name="Input 1"/>
+    <tableColumn id="4" xr3:uid="{F9C42DC7-57D1-4BB8-BBED-20B382C00DD4}" name="Input 2"/>
+    <tableColumn id="5" xr3:uid="{118DE43E-5FBD-4142-9FAB-89886CD01946}" name="Input 3"/>
+    <tableColumn id="6" xr3:uid="{C3D07E7B-98C0-439B-A814-7A278367C3E5}" name="Input 4"/>
+    <tableColumn id="7" xr3:uid="{C4F3128D-BAE2-4E30-AA79-51EA31A9EEAC}" name="Input 5"/>
+    <tableColumn id="8" xr3:uid="{CDBDC697-1755-4705-8EC1-A36F4F09035B}" name="Input 6"/>
+    <tableColumn id="9" xr3:uid="{C23862BE-4EEE-4C96-813B-4FF0DF16D364}" name="Input 7"/>
+    <tableColumn id="10" xr3:uid="{077BA596-874B-4082-BAE4-87ECA053BC3D}" name="Input 8"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3235" displayName="Table3235" ref="A1:J200" totalsRowShown="0">
   <autoFilter ref="A1:J200" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
@@ -1215,12 +1238,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A25:E26">
-    <cfRule type="expression" dxfId="21" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:F12 F13:F20 B15:E20 A21:F21 B22:F23">
-    <cfRule type="expression" dxfId="20" priority="3">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1231,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMK214"/>
+  <dimension ref="A1:AMK212"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="1" customWidth="1"/>
@@ -1679,7 +1702,7 @@
         <v>0.65</v>
       </c>
       <c r="F19" s="5">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G19" s="5">
         <v>0</v>
@@ -1722,7 +1745,7 @@
         <v>500</v>
       </c>
       <c r="E21" s="13">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F21" s="13">
         <v>0</v>
@@ -1841,14 +1864,20 @@
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -1856,14 +1885,20 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="14"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5">
-        <v>1000</v>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0</v>
+      </c>
+      <c r="G29" s="13"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="11"/>
@@ -1873,41 +1908,45 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="11"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="14"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5">
         <v>0</v>
       </c>
-      <c r="D31" s="13">
-        <v>1.2</v>
-      </c>
-      <c r="E31" s="13">
-        <v>0.08</v>
-      </c>
-      <c r="F31" s="13">
+      <c r="D31" s="5">
+        <v>5000</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="F31" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G31" s="5">
         <v>0</v>
       </c>
-      <c r="G31" s="13"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="11"/>
@@ -1942,16 +1981,16 @@
       <c r="A33" s="14"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D33" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E33" s="5">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="F33" s="5">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G33" s="5">
         <v>0</v>
@@ -1990,16 +2029,16 @@
       <c r="A35" s="14"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D35" s="5">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E35" s="5">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F35" s="5">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="G35" s="5">
         <v>0</v>
@@ -2038,16 +2077,16 @@
       <c r="A37" s="14"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="D37" s="5">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="E37" s="5">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="F37" s="5">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="G37" s="5">
         <v>0</v>
@@ -2086,16 +2125,16 @@
       <c r="A39" s="14"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="D39" s="5">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E39" s="5">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="F39" s="5">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="G39" s="5">
         <v>0</v>
@@ -2134,16 +2173,16 @@
       <c r="A41" s="14"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="D41" s="5">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="E41" s="5">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F41" s="5">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="G41" s="5">
         <v>0</v>
@@ -2182,16 +2221,16 @@
       <c r="A43" s="14"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="D43" s="5">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="E43" s="5">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="F43" s="5">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="G43" s="5">
         <v>0</v>
@@ -2205,45 +2244,41 @@
         <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="11"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="14"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5">
-        <v>30000</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="B45" s="12"/>
+      <c r="C45" s="13">
         <v>35000</v>
       </c>
-      <c r="E45" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="F45" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="G45" s="5">
+      <c r="D45" s="13">
+        <v>500</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F45" s="13">
         <v>0</v>
       </c>
+      <c r="G45" s="13"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="11"/>
@@ -2253,41 +2288,37 @@
         <v>23</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" s="3"/>
+      <c r="D46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="11"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="14"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="13">
-        <v>35000</v>
-      </c>
-      <c r="D47" s="13">
-        <v>500</v>
-      </c>
-      <c r="E47" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="F47" s="13">
+      <c r="B47" s="4"/>
+      <c r="C47" s="5">
+        <v>25000</v>
+      </c>
+      <c r="D47" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E47" s="5">
         <v>0</v>
       </c>
-      <c r="G47" s="13"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="11"/>
@@ -2297,37 +2328,29 @@
         <v>24</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="11"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="14"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="5">
-        <v>25000</v>
-      </c>
-      <c r="D49" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E49" s="5">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13">
+        <v>0.99</v>
+      </c>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="11"/>
@@ -2337,9 +2360,9 @@
         <v>25</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D50" s="3"/>
@@ -2352,32 +2375,26 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="14"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="13">
-        <v>0.99</v>
-      </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="4">
+        <v>0.999</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="11"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="14">
-        <v>26</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="11"/>
@@ -2385,9 +2402,7 @@
     <row r="53" spans="1:10">
       <c r="A53" s="14"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="4">
-        <v>0.999</v>
-      </c>
+      <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
@@ -2434,24 +2449,24 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="14"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="11"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="14"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="11"/>
@@ -2506,24 +2521,24 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="14"/>
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="11"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="14"/>
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="11"/>
@@ -4293,74 +4308,50 @@
       <c r="J211" s="11"/>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="14"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="5"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
-      <c r="H212" s="5"/>
-      <c r="I212" s="5"/>
-      <c r="J212" s="11"/>
-    </row>
-    <row r="213" spans="1:10">
-      <c r="A213" s="14"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
-      <c r="D213" s="5"/>
-      <c r="E213" s="5"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
-      <c r="H213" s="5"/>
-      <c r="I213" s="5"/>
-      <c r="J213" s="11"/>
-    </row>
-    <row r="214" spans="1:10">
-      <c r="A214" s="15"/>
-      <c r="B214" s="16"/>
-      <c r="C214" s="16"/>
-      <c r="D214" s="16"/>
-      <c r="E214" s="16"/>
-      <c r="F214" s="16"/>
-      <c r="G214" s="16"/>
-      <c r="H214" s="16"/>
-      <c r="I214" s="16"/>
-      <c r="J214" s="17"/>
+      <c r="A212" s="15"/>
+      <c r="B212" s="16"/>
+      <c r="C212" s="16"/>
+      <c r="D212" s="16"/>
+      <c r="E212" s="16"/>
+      <c r="F212" s="16"/>
+      <c r="G212" s="16"/>
+      <c r="H212" s="16"/>
+      <c r="I212" s="16"/>
+      <c r="J212" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2 H2:AMJ27 K28:AMJ1048576 A54:J58 H59:J64 A65:J1048576 H28:J53 C24:G31 A28:A53 C46:G47 C32:D45 G32:G45">
-    <cfRule type="expression" dxfId="19" priority="5">
+  <conditionalFormatting sqref="A1:A2 H2:AMJ27 C24:G29 H28:J51 A28:A52 K28:AMJ1048576 C30:D43 G30:G43 C44:G45 A52:J56 H57:J62 A63:J1048576">
+    <cfRule type="expression" dxfId="20" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="18" priority="6">
+    <cfRule type="expression" dxfId="19" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G5 C20:G21 C6:D19 G6:G19">
-    <cfRule type="expression" dxfId="17" priority="8">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G23 G48:G49 C50:G53">
-    <cfRule type="expression" dxfId="16" priority="9">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1:AMJ1 A59:A64">
-    <cfRule type="expression" dxfId="15" priority="7">
+  <conditionalFormatting sqref="C2:G5 C6:D19 G6:G19 C20:G21">
+    <cfRule type="expression" dxfId="18" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:F19">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32:F45">
-    <cfRule type="expression" dxfId="6" priority="1">
+  <conditionalFormatting sqref="E30:F43">
+    <cfRule type="expression" dxfId="16" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G23 G46:G47 C48:G51">
+    <cfRule type="expression" dxfId="15" priority="9">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:AMJ1 A57:A62">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4373,6 +4364,3149 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BA2653E-7E99-4047-B201-5BD44C2A87ED}">
+  <dimension ref="A1:AMK214"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="15.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.69921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" style="1" customWidth="1"/>
+    <col min="8" max="1025" width="10.796875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16.2" thickBot="1">
+      <c r="A1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="10"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4">
+        <v>0.995</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="F5" s="13">
+        <v>0</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="10">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="10"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="10">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="10"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="10">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="10"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="10">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="10"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5">
+        <v>15000</v>
+      </c>
+      <c r="D13" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="10">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="10"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5">
+        <v>20000</v>
+      </c>
+      <c r="D15" s="5">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="10">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="10"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5">
+        <v>25000</v>
+      </c>
+      <c r="D17" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="10">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="10"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5">
+        <v>30000</v>
+      </c>
+      <c r="D19" s="5">
+        <v>35000</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="10">
+        <v>10</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="10"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13">
+        <v>35000</v>
+      </c>
+      <c r="D21" s="13">
+        <v>500</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="10">
+        <v>11</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="10"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="5">
+        <v>25000</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="11"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="10">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="11"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="10"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13">
+        <v>0.99</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="11"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="10">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="14"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="4">
+        <v>0.999</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="14">
+        <v>14</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="11"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="14"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="5">
+        <v>1000</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="11"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="14">
+        <v>15</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="11"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="14"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="F31" s="13">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="11"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="14">
+        <v>16</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="14"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5">
+        <v>5000</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="14">
+        <v>17</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="14"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5">
+        <v>5000</v>
+      </c>
+      <c r="D35" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F35" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G35" s="5">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="14">
+        <v>18</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="14"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5">
+        <v>10000</v>
+      </c>
+      <c r="D37" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F37" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="G37" s="5">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="14">
+        <v>19</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="14"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5">
+        <v>15000</v>
+      </c>
+      <c r="D39" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="F39" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="14">
+        <v>20</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="14"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5">
+        <v>20000</v>
+      </c>
+      <c r="D41" s="5">
+        <v>25000</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F41" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="14">
+        <v>21</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="14"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5">
+        <v>25000</v>
+      </c>
+      <c r="D43" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="F43" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="14">
+        <v>22</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="14"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5">
+        <v>30000</v>
+      </c>
+      <c r="D45" s="5">
+        <v>35000</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="F45" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="14">
+        <v>23</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" s="3"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="14"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13">
+        <v>35000</v>
+      </c>
+      <c r="D47" s="13">
+        <v>500</v>
+      </c>
+      <c r="E47" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="F47" s="13">
+        <v>0</v>
+      </c>
+      <c r="G47" s="13"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="14">
+        <v>24</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="14"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="5">
+        <v>25000</v>
+      </c>
+      <c r="D49" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E49" s="5">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="14">
+        <v>25</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="14"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="13">
+        <v>0.99</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="11"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="14">
+        <v>26</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="11"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="14"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="4">
+        <v>0.999</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="11"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="14"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="11"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="14"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="11"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="14"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="11"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="14"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="11"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="14"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="14"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="11"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="14"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="11"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="14"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="11"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="14"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="11"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="14"/>
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="11"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="14"/>
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="14"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="14"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="14"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="11"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="14"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="11"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="14"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="11"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="14"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="11"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="14"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="11"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="14"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="11"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="14"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="11"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="14"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="11"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="14"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="11"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="14"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="11"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="14"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="11"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="14"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="11"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="14"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="11"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="14"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="11"/>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="14"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="11"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="14"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="11"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="14"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="11"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="14"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="11"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="14"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="11"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="14"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="11"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="14"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="11"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="14"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="11"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="14"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="11"/>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="14"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="11"/>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="14"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="11"/>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="14"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="11"/>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="14"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="11"/>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="14"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="11"/>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="14"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="11"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="14"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="11"/>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="14"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="11"/>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="14"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="11"/>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="14"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="11"/>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="14"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="11"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="14"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="11"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="14"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="11"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="14"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="11"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="14"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="11"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="14"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="11"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="14"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="11"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="14"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="11"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="14"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="11"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="14"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="11"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="14"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="11"/>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="14"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="11"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="14"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="11"/>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="14"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="11"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="14"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="11"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="14"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="11"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" s="14"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="11"/>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="14"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="11"/>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="14"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="11"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="14"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="11"/>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" s="14"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="11"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" s="14"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="11"/>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" s="14"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="11"/>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" s="14"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="5"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="11"/>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" s="14"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="11"/>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" s="14"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="5"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="11"/>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" s="14"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="11"/>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" s="14"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="11"/>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" s="14"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="5"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="11"/>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="14"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="11"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="14"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="11"/>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" s="14"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+      <c r="I131" s="5"/>
+      <c r="J131" s="11"/>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="14"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5"/>
+      <c r="J132" s="11"/>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="14"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+      <c r="I133" s="5"/>
+      <c r="J133" s="11"/>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" s="14"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="11"/>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" s="14"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="11"/>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" s="14"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="5"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+      <c r="I136" s="5"/>
+      <c r="J136" s="11"/>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" s="14"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="11"/>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" s="14"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="11"/>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" s="14"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="5"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="11"/>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" s="14"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="5"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="11"/>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" s="14"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="5"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="11"/>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" s="14"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="11"/>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" s="14"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="5"/>
+      <c r="D143" s="5"/>
+      <c r="E143" s="5"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="11"/>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" s="14"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="5"/>
+      <c r="E144" s="5"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="11"/>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" s="14"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="11"/>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" s="14"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="11"/>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" s="14"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="11"/>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" s="14"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="11"/>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" s="14"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="5"/>
+      <c r="E149" s="5"/>
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="11"/>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" s="14"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="11"/>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" s="14"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="11"/>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152" s="14"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="11"/>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153" s="14"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5"/>
+      <c r="J153" s="11"/>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154" s="14"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="11"/>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" s="14"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="11"/>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156" s="14"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="5"/>
+      <c r="E156" s="5"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="11"/>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157" s="14"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="11"/>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" s="14"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="5"/>
+      <c r="E158" s="5"/>
+      <c r="F158" s="5"/>
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+      <c r="I158" s="5"/>
+      <c r="J158" s="11"/>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159" s="14"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="5"/>
+      <c r="J159" s="11"/>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160" s="14"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5"/>
+      <c r="G160" s="5"/>
+      <c r="H160" s="5"/>
+      <c r="I160" s="5"/>
+      <c r="J160" s="11"/>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" s="14"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="5"/>
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
+      <c r="I161" s="5"/>
+      <c r="J161" s="11"/>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" s="14"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="5"/>
+      <c r="E162" s="5"/>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
+      <c r="H162" s="5"/>
+      <c r="I162" s="5"/>
+      <c r="J162" s="11"/>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" s="14"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="5"/>
+      <c r="D163" s="5"/>
+      <c r="E163" s="5"/>
+      <c r="F163" s="5"/>
+      <c r="G163" s="5"/>
+      <c r="H163" s="5"/>
+      <c r="I163" s="5"/>
+      <c r="J163" s="11"/>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" s="14"/>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="5"/>
+      <c r="E164" s="5"/>
+      <c r="F164" s="5"/>
+      <c r="G164" s="5"/>
+      <c r="H164" s="5"/>
+      <c r="I164" s="5"/>
+      <c r="J164" s="11"/>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165" s="14"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="5"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+      <c r="H165" s="5"/>
+      <c r="I165" s="5"/>
+      <c r="J165" s="11"/>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166" s="14"/>
+      <c r="B166" s="5"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="5"/>
+      <c r="J166" s="11"/>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167" s="14"/>
+      <c r="B167" s="5"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="5"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
+      <c r="H167" s="5"/>
+      <c r="I167" s="5"/>
+      <c r="J167" s="11"/>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168" s="14"/>
+      <c r="B168" s="5"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="5"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
+      <c r="H168" s="5"/>
+      <c r="I168" s="5"/>
+      <c r="J168" s="11"/>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169" s="14"/>
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
+      <c r="J169" s="11"/>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170" s="14"/>
+      <c r="B170" s="5"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5"/>
+      <c r="J170" s="11"/>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171" s="14"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="5"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
+      <c r="I171" s="5"/>
+      <c r="J171" s="11"/>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172" s="14"/>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
+      <c r="H172" s="5"/>
+      <c r="I172" s="5"/>
+      <c r="J172" s="11"/>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173" s="14"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
+      <c r="I173" s="5"/>
+      <c r="J173" s="11"/>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174" s="14"/>
+      <c r="B174" s="5"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5"/>
+      <c r="J174" s="11"/>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175" s="14"/>
+      <c r="B175" s="5"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5"/>
+      <c r="J175" s="11"/>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176" s="14"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
+      <c r="J176" s="11"/>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177" s="14"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="5"/>
+      <c r="D177" s="5"/>
+      <c r="E177" s="5"/>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
+      <c r="H177" s="5"/>
+      <c r="I177" s="5"/>
+      <c r="J177" s="11"/>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178" s="14"/>
+      <c r="B178" s="5"/>
+      <c r="C178" s="5"/>
+      <c r="D178" s="5"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="5"/>
+      <c r="G178" s="5"/>
+      <c r="H178" s="5"/>
+      <c r="I178" s="5"/>
+      <c r="J178" s="11"/>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179" s="14"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="5"/>
+      <c r="E179" s="5"/>
+      <c r="F179" s="5"/>
+      <c r="G179" s="5"/>
+      <c r="H179" s="5"/>
+      <c r="I179" s="5"/>
+      <c r="J179" s="11"/>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180" s="14"/>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
+      <c r="D180" s="5"/>
+      <c r="E180" s="5"/>
+      <c r="F180" s="5"/>
+      <c r="G180" s="5"/>
+      <c r="H180" s="5"/>
+      <c r="I180" s="5"/>
+      <c r="J180" s="11"/>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" s="14"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="5"/>
+      <c r="D181" s="5"/>
+      <c r="E181" s="5"/>
+      <c r="F181" s="5"/>
+      <c r="G181" s="5"/>
+      <c r="H181" s="5"/>
+      <c r="I181" s="5"/>
+      <c r="J181" s="11"/>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" s="14"/>
+      <c r="B182" s="5"/>
+      <c r="C182" s="5"/>
+      <c r="D182" s="5"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="5"/>
+      <c r="G182" s="5"/>
+      <c r="H182" s="5"/>
+      <c r="I182" s="5"/>
+      <c r="J182" s="11"/>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183" s="14"/>
+      <c r="B183" s="5"/>
+      <c r="C183" s="5"/>
+      <c r="D183" s="5"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="5"/>
+      <c r="G183" s="5"/>
+      <c r="H183" s="5"/>
+      <c r="I183" s="5"/>
+      <c r="J183" s="11"/>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184" s="14"/>
+      <c r="B184" s="5"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="5"/>
+      <c r="E184" s="5"/>
+      <c r="F184" s="5"/>
+      <c r="G184" s="5"/>
+      <c r="H184" s="5"/>
+      <c r="I184" s="5"/>
+      <c r="J184" s="11"/>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" s="14"/>
+      <c r="B185" s="5"/>
+      <c r="C185" s="5"/>
+      <c r="D185" s="5"/>
+      <c r="E185" s="5"/>
+      <c r="F185" s="5"/>
+      <c r="G185" s="5"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="5"/>
+      <c r="J185" s="11"/>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" s="14"/>
+      <c r="B186" s="5"/>
+      <c r="C186" s="5"/>
+      <c r="D186" s="5"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="5"/>
+      <c r="G186" s="5"/>
+      <c r="H186" s="5"/>
+      <c r="I186" s="5"/>
+      <c r="J186" s="11"/>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187" s="14"/>
+      <c r="B187" s="5"/>
+      <c r="C187" s="5"/>
+      <c r="D187" s="5"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="5"/>
+      <c r="G187" s="5"/>
+      <c r="H187" s="5"/>
+      <c r="I187" s="5"/>
+      <c r="J187" s="11"/>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188" s="14"/>
+      <c r="B188" s="5"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="5"/>
+      <c r="J188" s="11"/>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189" s="14"/>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="5"/>
+      <c r="J189" s="11"/>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190" s="14"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="5"/>
+      <c r="D190" s="5"/>
+      <c r="E190" s="5"/>
+      <c r="F190" s="5"/>
+      <c r="G190" s="5"/>
+      <c r="H190" s="5"/>
+      <c r="I190" s="5"/>
+      <c r="J190" s="11"/>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191" s="14"/>
+      <c r="B191" s="5"/>
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5"/>
+      <c r="G191" s="5"/>
+      <c r="H191" s="5"/>
+      <c r="I191" s="5"/>
+      <c r="J191" s="11"/>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192" s="14"/>
+      <c r="B192" s="5"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="5"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+      <c r="H192" s="5"/>
+      <c r="I192" s="5"/>
+      <c r="J192" s="11"/>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" s="14"/>
+      <c r="B193" s="5"/>
+      <c r="C193" s="5"/>
+      <c r="D193" s="5"/>
+      <c r="E193" s="5"/>
+      <c r="F193" s="5"/>
+      <c r="G193" s="5"/>
+      <c r="H193" s="5"/>
+      <c r="I193" s="5"/>
+      <c r="J193" s="11"/>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" s="14"/>
+      <c r="B194" s="5"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="5"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="5"/>
+      <c r="J194" s="11"/>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195" s="14"/>
+      <c r="B195" s="5"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5"/>
+      <c r="J195" s="11"/>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196" s="14"/>
+      <c r="B196" s="5"/>
+      <c r="C196" s="5"/>
+      <c r="D196" s="5"/>
+      <c r="E196" s="5"/>
+      <c r="F196" s="5"/>
+      <c r="G196" s="5"/>
+      <c r="H196" s="5"/>
+      <c r="I196" s="5"/>
+      <c r="J196" s="11"/>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197" s="14"/>
+      <c r="B197" s="5"/>
+      <c r="C197" s="5"/>
+      <c r="D197" s="5"/>
+      <c r="E197" s="5"/>
+      <c r="F197" s="5"/>
+      <c r="G197" s="5"/>
+      <c r="H197" s="5"/>
+      <c r="I197" s="5"/>
+      <c r="J197" s="11"/>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" s="14"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="5"/>
+      <c r="D198" s="5"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="5"/>
+      <c r="H198" s="5"/>
+      <c r="I198" s="5"/>
+      <c r="J198" s="11"/>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199" s="14"/>
+      <c r="B199" s="5"/>
+      <c r="C199" s="5"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+      <c r="H199" s="5"/>
+      <c r="I199" s="5"/>
+      <c r="J199" s="11"/>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200" s="14"/>
+      <c r="B200" s="5"/>
+      <c r="C200" s="5"/>
+      <c r="D200" s="5"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+      <c r="H200" s="5"/>
+      <c r="I200" s="5"/>
+      <c r="J200" s="11"/>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="A201" s="14"/>
+      <c r="B201" s="5"/>
+      <c r="C201" s="5"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
+      <c r="H201" s="5"/>
+      <c r="I201" s="5"/>
+      <c r="J201" s="11"/>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202" s="14"/>
+      <c r="B202" s="5"/>
+      <c r="C202" s="5"/>
+      <c r="D202" s="5"/>
+      <c r="E202" s="5"/>
+      <c r="F202" s="5"/>
+      <c r="G202" s="5"/>
+      <c r="H202" s="5"/>
+      <c r="I202" s="5"/>
+      <c r="J202" s="11"/>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="A203" s="14"/>
+      <c r="B203" s="5"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="5"/>
+      <c r="H203" s="5"/>
+      <c r="I203" s="5"/>
+      <c r="J203" s="11"/>
+    </row>
+    <row r="204" spans="1:10">
+      <c r="A204" s="14"/>
+      <c r="B204" s="5"/>
+      <c r="C204" s="5"/>
+      <c r="D204" s="5"/>
+      <c r="E204" s="5"/>
+      <c r="F204" s="5"/>
+      <c r="G204" s="5"/>
+      <c r="H204" s="5"/>
+      <c r="I204" s="5"/>
+      <c r="J204" s="11"/>
+    </row>
+    <row r="205" spans="1:10">
+      <c r="A205" s="14"/>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
+      <c r="D205" s="5"/>
+      <c r="E205" s="5"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
+      <c r="I205" s="5"/>
+      <c r="J205" s="11"/>
+    </row>
+    <row r="206" spans="1:10">
+      <c r="A206" s="14"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="5"/>
+      <c r="D206" s="5"/>
+      <c r="E206" s="5"/>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+      <c r="H206" s="5"/>
+      <c r="I206" s="5"/>
+      <c r="J206" s="11"/>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207" s="14"/>
+      <c r="B207" s="5"/>
+      <c r="C207" s="5"/>
+      <c r="D207" s="5"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+      <c r="I207" s="5"/>
+      <c r="J207" s="11"/>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208" s="14"/>
+      <c r="B208" s="5"/>
+      <c r="C208" s="5"/>
+      <c r="D208" s="5"/>
+      <c r="E208" s="5"/>
+      <c r="F208" s="5"/>
+      <c r="G208" s="5"/>
+      <c r="H208" s="5"/>
+      <c r="I208" s="5"/>
+      <c r="J208" s="11"/>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209" s="14"/>
+      <c r="B209" s="5"/>
+      <c r="C209" s="5"/>
+      <c r="D209" s="5"/>
+      <c r="E209" s="5"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="5"/>
+      <c r="H209" s="5"/>
+      <c r="I209" s="5"/>
+      <c r="J209" s="11"/>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210" s="14"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="5"/>
+      <c r="D210" s="5"/>
+      <c r="E210" s="5"/>
+      <c r="F210" s="5"/>
+      <c r="G210" s="5"/>
+      <c r="H210" s="5"/>
+      <c r="I210" s="5"/>
+      <c r="J210" s="11"/>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211" s="14"/>
+      <c r="B211" s="5"/>
+      <c r="C211" s="5"/>
+      <c r="D211" s="5"/>
+      <c r="E211" s="5"/>
+      <c r="F211" s="5"/>
+      <c r="G211" s="5"/>
+      <c r="H211" s="5"/>
+      <c r="I211" s="5"/>
+      <c r="J211" s="11"/>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212" s="14"/>
+      <c r="B212" s="5"/>
+      <c r="C212" s="5"/>
+      <c r="D212" s="5"/>
+      <c r="E212" s="5"/>
+      <c r="F212" s="5"/>
+      <c r="G212" s="5"/>
+      <c r="H212" s="5"/>
+      <c r="I212" s="5"/>
+      <c r="J212" s="11"/>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213" s="14"/>
+      <c r="B213" s="5"/>
+      <c r="C213" s="5"/>
+      <c r="D213" s="5"/>
+      <c r="E213" s="5"/>
+      <c r="F213" s="5"/>
+      <c r="G213" s="5"/>
+      <c r="H213" s="5"/>
+      <c r="I213" s="5"/>
+      <c r="J213" s="11"/>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214" s="15"/>
+      <c r="B214" s="16"/>
+      <c r="C214" s="16"/>
+      <c r="D214" s="16"/>
+      <c r="E214" s="16"/>
+      <c r="F214" s="16"/>
+      <c r="G214" s="16"/>
+      <c r="H214" s="16"/>
+      <c r="I214" s="16"/>
+      <c r="J214" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A2 H2:AMJ27 C24:G31 A28:A53 H28:J53 K28:AMJ1048576 C32:D45 G32:G45 C46:G47 A54:J58 H59:J64 A65:J1048576">
+    <cfRule type="expression" dxfId="13" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1 D1:J1">
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G5 C6:D19 G6:G19 C20:G21">
+    <cfRule type="expression" dxfId="11" priority="6">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:F19">
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32:F45">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G23 G48:G49 C50:G53">
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:AMJ1 A59:A64">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AMK200"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -6948,37 +10082,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2 F2:AMJ3 B2:E11 H4:AMJ7 G8:AMJ11 F12:AMJ19">
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:D13">
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:E15">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F11">
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G7">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:AMJ1 E20:AMJ21 A22:AMJ1048576">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Mission Profiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9EE423-0FE6-41AF-A94F-2A67136B10F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ABB1E8-A460-4029-AD8D-D258E7D43C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1365,7 +1365,7 @@
         <v>1.2</v>
       </c>
       <c r="E5" s="13">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="13">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>1.2</v>
       </c>
       <c r="E29" s="13">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="F29" s="13">
         <v>0</v>

--- a/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Mission Profiles/Mission_Profile_Jet.xlsx
@@ -1,36 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Mission Profiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ABB1E8-A460-4029-AD8D-D258E7D43C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Templates" sheetId="1" r:id="rId1"/>
-    <sheet name="JetSubmersible" sheetId="2" r:id="rId2"/>
-    <sheet name="JetSubmersibleDrop" sheetId="5" r:id="rId3"/>
-    <sheet name="Electric C172" sheetId="4" r:id="rId4"/>
+    <sheet name="Templates" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="JetSubmersible" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="JetSubmersibleDrop" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Electric C172" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -41,137 +25,154 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="39">
   <si>
-    <t>Startup/Taxi</t>
+    <t xml:space="preserve">Startup/Taxi</t>
   </si>
   <si>
-    <t>Weight Fraction</t>
+    <t xml:space="preserve">Weight Fraction</t>
   </si>
   <si>
-    <t>Takeoff</t>
+    <t xml:space="preserve">Takeoff</t>
   </si>
   <si>
     <t xml:space="preserve">Altitude [ft] </t>
   </si>
   <si>
-    <t>Cl Max</t>
+    <t xml:space="preserve">Cl Max</t>
   </si>
   <si>
-    <t>Coef Friction</t>
+    <t xml:space="preserve">Coef Friction</t>
   </si>
   <si>
-    <t>CDx_TO</t>
+    <t xml:space="preserve">CDx_TO</t>
   </si>
   <si>
-    <t>Climb</t>
+    <t xml:space="preserve">Climb</t>
   </si>
   <si>
-    <t>Start Altitude [ft]</t>
+    <t xml:space="preserve">Start Altitude [ft]</t>
   </si>
   <si>
-    <t>End Altitude [ft]</t>
+    <t xml:space="preserve">End Altitude [ft]</t>
   </si>
   <si>
-    <t>Start Mach</t>
+    <t xml:space="preserve">Start Mach</t>
   </si>
   <si>
-    <t>End Mach</t>
+    <t xml:space="preserve">End Mach</t>
   </si>
   <si>
-    <t>CDx_Climb</t>
+    <t xml:space="preserve">CDx_Climb</t>
   </si>
   <si>
-    <t>Cruise</t>
+    <t xml:space="preserve">Cruise</t>
   </si>
   <si>
-    <t>Altitude [ft]</t>
+    <t xml:space="preserve">Altitude [ft]</t>
   </si>
   <si>
-    <t>Range [nm]</t>
+    <t xml:space="preserve">Range [nm]</t>
   </si>
   <si>
-    <t>Mach</t>
+    <t xml:space="preserve">Mach</t>
   </si>
   <si>
-    <t>CDx_Cruise</t>
+    <t xml:space="preserve">CDx_Cruise</t>
   </si>
   <si>
-    <t>Loiter</t>
+    <t xml:space="preserve">Loiter</t>
   </si>
   <si>
-    <t>Loiter Time [hr]</t>
+    <t xml:space="preserve">Loiter Time [hr]</t>
   </si>
   <si>
-    <t>CDx_Loiter</t>
+    <t xml:space="preserve">CDx_Loiter</t>
   </si>
   <si>
-    <t>Descent</t>
+    <t xml:space="preserve">Descent</t>
   </si>
   <si>
-    <t>Landing</t>
+    <t xml:space="preserve">Landing</t>
   </si>
   <si>
-    <t>Drop</t>
+    <t xml:space="preserve">Drop</t>
   </si>
   <si>
-    <t>Payload Dropped [lbs]</t>
+    <t xml:space="preserve">Payload Dropped [lbs]</t>
   </si>
   <si>
-    <t>VTOL</t>
+    <t xml:space="preserve">VTOL</t>
   </si>
   <si>
-    <t>Hover Time [s]</t>
+    <t xml:space="preserve">Hover Time [s]</t>
   </si>
   <si>
-    <t>Altitude Gain [ft]</t>
+    <t xml:space="preserve">Altitude Gain [ft]</t>
   </si>
   <si>
-    <t>Segment #</t>
+    <t xml:space="preserve">Segment #</t>
   </si>
   <si>
-    <t>Segment Type</t>
+    <t xml:space="preserve">Segment Type</t>
   </si>
   <si>
-    <t>Input 1</t>
+    <t xml:space="preserve">Input 1</t>
   </si>
   <si>
-    <t>Input 2</t>
+    <t xml:space="preserve">Input 2</t>
   </si>
   <si>
-    <t>Input 3</t>
+    <t xml:space="preserve">Input 3</t>
   </si>
   <si>
-    <t>Input 4</t>
+    <t xml:space="preserve">Input 4</t>
   </si>
   <si>
-    <t>Input 5</t>
+    <t xml:space="preserve">Input 5</t>
   </si>
   <si>
-    <t>Input 6</t>
+    <t xml:space="preserve">Input 6</t>
   </si>
   <si>
-    <t>Input 7</t>
+    <t xml:space="preserve">Input 7</t>
   </si>
   <si>
-    <t>Input 8</t>
+    <t xml:space="preserve">Input 8</t>
   </si>
   <si>
-    <t>BMF</t>
+    <t xml:space="preserve">BMF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -181,17 +182,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -217,243 +211,219 @@
     </fill>
   </fills>
   <borders count="10">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="17" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -512,413 +482,82 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table32352" displayName="Table32352" ref="A1:J212" totalsRowShown="0">
-  <autoFilter ref="A1:J212" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3235" displayName="Table3235" ref="A1:J200" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J200"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Segment #"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Segment Type"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Input 1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Input 2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Input 3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Input 4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Input 5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Input 6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Input 7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Input 8"/>
+    <tableColumn id="1" name="Segment #"/>
+    <tableColumn id="2" name="Segment Type"/>
+    <tableColumn id="3" name="Input 1"/>
+    <tableColumn id="4" name="Input 2"/>
+    <tableColumn id="5" name="Input 3"/>
+    <tableColumn id="6" name="Input 4"/>
+    <tableColumn id="7" name="Input 5"/>
+    <tableColumn id="8" name="Input 6"/>
+    <tableColumn id="9" name="Input 7"/>
+    <tableColumn id="10" name="Input 8"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AE63C51F-3251-414D-B554-0C05CDF493D6}" name="Table323524" displayName="Table323524" ref="A1:J214" totalsRowShown="0">
-  <autoFilter ref="A1:J214" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table32352" displayName="Table32352" ref="A1:J212" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J212"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{4659FCE2-E25D-48AA-89F4-F0BBB5B587AC}" name="Segment #"/>
-    <tableColumn id="2" xr3:uid="{58B7FC18-0858-4DEA-ACC7-3666A9454C35}" name="Segment Type"/>
-    <tableColumn id="3" xr3:uid="{C3ECEC8F-EAC9-42CD-8DC6-92703EDAEDCB}" name="Input 1"/>
-    <tableColumn id="4" xr3:uid="{F9C42DC7-57D1-4BB8-BBED-20B382C00DD4}" name="Input 2"/>
-    <tableColumn id="5" xr3:uid="{118DE43E-5FBD-4142-9FAB-89886CD01946}" name="Input 3"/>
-    <tableColumn id="6" xr3:uid="{C3D07E7B-98C0-439B-A814-7A278367C3E5}" name="Input 4"/>
-    <tableColumn id="7" xr3:uid="{C4F3128D-BAE2-4E30-AA79-51EA31A9EEAC}" name="Input 5"/>
-    <tableColumn id="8" xr3:uid="{CDBDC697-1755-4705-8EC1-A36F4F09035B}" name="Input 6"/>
-    <tableColumn id="9" xr3:uid="{C23862BE-4EEE-4C96-813B-4FF0DF16D364}" name="Input 7"/>
-    <tableColumn id="10" xr3:uid="{077BA596-874B-4082-BAE4-87ECA053BC3D}" name="Input 8"/>
+    <tableColumn id="1" name="Segment #"/>
+    <tableColumn id="2" name="Segment Type"/>
+    <tableColumn id="3" name="Input 1"/>
+    <tableColumn id="4" name="Input 2"/>
+    <tableColumn id="5" name="Input 3"/>
+    <tableColumn id="6" name="Input 4"/>
+    <tableColumn id="7" name="Input 5"/>
+    <tableColumn id="8" name="Input 6"/>
+    <tableColumn id="9" name="Input 7"/>
+    <tableColumn id="10" name="Input 8"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3235" displayName="Table3235" ref="A1:J200" totalsRowShown="0">
-  <autoFilter ref="A1:J200" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table323524" displayName="Table323524" ref="A1:J214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J214"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Segment #"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Segment Type"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Input 1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Input 2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Input 3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Input 4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Input 5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Input 6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Input 7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Input 8"/>
+    <tableColumn id="1" name="Segment #"/>
+    <tableColumn id="2" name="Segment Type"/>
+    <tableColumn id="3" name="Input 1"/>
+    <tableColumn id="4" name="Input 2"/>
+    <tableColumn id="5" name="Input 3"/>
+    <tableColumn id="6" name="Input 4"/>
+    <tableColumn id="7" name="Input 5"/>
+    <tableColumn id="8" name="Input 6"/>
+    <tableColumn id="9" name="Input 7"/>
+    <tableColumn id="10" name="Input 8"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMK26"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15.6" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="20.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="20.796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="1025" width="10.796875" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="7" style="1" width="10.8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -930,9 +569,9 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
-      <c r="B2" s="4">
+      <c r="B2" s="4" t="n">
         <v>0.995</v>
       </c>
       <c r="C2" s="5"/>
@@ -940,7 +579,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -948,7 +587,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -966,23 +605,23 @@
       </c>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
-      <c r="B5" s="3">
+      <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -990,7 +629,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" s="6" customFormat="1">
+    <row r="7" s="6" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1010,25 +649,25 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
-      <c r="B8" s="5">
+      <c r="B8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1036,7 +675,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -1054,23 +693,23 @@
       </c>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
-      <c r="B11" s="3">
+      <c r="B11" s="3" t="n">
         <v>38000</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1078,7 +717,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" s="6" customFormat="1">
+    <row r="13" s="6" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -1094,21 +733,21 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
-      <c r="B14" s="5">
+      <c r="B14" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1116,7 +755,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>21</v>
       </c>
@@ -1128,9 +767,9 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
-      <c r="B17" s="3">
+      <c r="B17" s="3" t="n">
         <v>0.99</v>
       </c>
       <c r="C17" s="3"/>
@@ -1138,7 +777,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1146,7 +785,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -1158,9 +797,9 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
-      <c r="B20" s="4">
+      <c r="B20" s="4" t="n">
         <v>0.999</v>
       </c>
       <c r="C20" s="5"/>
@@ -1168,7 +807,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1176,7 +815,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
@@ -1188,9 +827,9 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
-      <c r="B23" s="5">
+      <c r="B23" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="C23" s="5"/>
@@ -1198,7 +837,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1206,7 +845,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
@@ -1222,15 +861,15 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
-      <c r="B26" s="3">
+      <c r="B26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="n">
         <v>250</v>
       </c>
       <c r="E26" s="3"/>
@@ -1238,36 +877,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A25:E26">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:F12 F13:F20 B15:E20 A21:F21 B22:F23">
-    <cfRule type="expression" dxfId="21" priority="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMK212"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J212"/>
+  <sheetFormatPr defaultRowHeight="15.6" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.19921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.796875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" style="1" customWidth="1"/>
-    <col min="8" max="1025" width="10.796875" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="1" width="10.8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
@@ -1299,8 +946,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7">
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1317,10 +964,10 @@
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="4">
+      <c r="C3" s="4" t="n">
         <v>0.995</v>
       </c>
       <c r="D3" s="5"/>
@@ -1331,8 +978,8 @@
       <c r="I3" s="5"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="10">
+    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1355,19 +1002,19 @@
       <c r="I4" s="5"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="13">
+      <c r="C5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="13"/>
@@ -1375,8 +1022,8 @@
       <c r="I5" s="5"/>
       <c r="J5" s="11"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="10">
+    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1401,30 +1048,30 @@
       <c r="I6" s="5"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="11"/>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="10">
+    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1449,30 +1096,30 @@
       <c r="I8" s="5"/>
       <c r="J8" s="11"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="5">
+      <c r="C9" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="11"/>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="10">
+    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1497,30 +1144,30 @@
       <c r="I10" s="5"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="5">
+      <c r="C11" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="11"/>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="10">
+    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1545,30 +1192,30 @@
       <c r="I12" s="5"/>
       <c r="J12" s="11"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="5">
+      <c r="C13" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="11"/>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="10">
+    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1593,30 +1240,30 @@
       <c r="I14" s="5"/>
       <c r="J14" s="11"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="5">
+      <c r="C15" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="11"/>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="10">
+    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1641,30 +1288,30 @@
       <c r="I16" s="5"/>
       <c r="J16" s="11"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="5">
+      <c r="C17" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="11"/>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="10">
+    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1689,30 +1336,30 @@
       <c r="I18" s="5"/>
       <c r="J18" s="11"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="5">
+      <c r="C19" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="5" t="n">
         <v>35000</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="11"/>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="10">
+    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="n">
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1735,19 +1382,19 @@
       <c r="I20" s="5"/>
       <c r="J20" s="11"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
       <c r="B21" s="12"/>
-      <c r="C21" s="13">
+      <c r="C21" s="13" t="n">
         <v>35000</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="13"/>
@@ -1755,8 +1402,8 @@
       <c r="I21" s="5"/>
       <c r="J21" s="11"/>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="10">
+    <row r="22" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="n">
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1777,16 +1424,16 @@
       <c r="I22" s="5"/>
       <c r="J22" s="11"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="5">
+      <c r="C23" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="5"/>
@@ -1795,8 +1442,8 @@
       <c r="I23" s="5"/>
       <c r="J23" s="11"/>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="10">
+    <row r="24" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="n">
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1813,10 +1460,10 @@
       <c r="I24" s="5"/>
       <c r="J24" s="11"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
       <c r="B25" s="12"/>
-      <c r="C25" s="13">
+      <c r="C25" s="13" t="n">
         <v>0.99</v>
       </c>
       <c r="D25" s="13"/>
@@ -1827,8 +1474,8 @@
       <c r="I25" s="5"/>
       <c r="J25" s="11"/>
     </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="10">
+    <row r="26" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="n">
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1845,10 +1492,10 @@
       <c r="I26" s="5"/>
       <c r="J26" s="11"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="4">
+      <c r="C27" s="4" t="n">
         <v>0.999</v>
       </c>
       <c r="D27" s="5"/>
@@ -1859,8 +1506,8 @@
       <c r="I27" s="5"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="14">
+    <row r="28" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1883,19 +1530,19 @@
       <c r="I28" s="5"/>
       <c r="J28" s="11"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14"/>
       <c r="B29" s="12"/>
-      <c r="C29" s="13">
+      <c r="C29" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="13"/>
@@ -1903,8 +1550,8 @@
       <c r="I29" s="5"/>
       <c r="J29" s="11"/>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="14">
+    <row r="30" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1929,30 +1576,30 @@
       <c r="I30" s="5"/>
       <c r="J30" s="11"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="5">
+      <c r="C31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="11"/>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="14">
+    <row r="32" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -1977,30 +1624,30 @@
       <c r="I32" s="5"/>
       <c r="J32" s="11"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="5">
+      <c r="C33" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="11"/>
     </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="14">
+    <row r="34" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -2025,30 +1672,30 @@
       <c r="I34" s="5"/>
       <c r="J34" s="11"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="5">
+      <c r="C35" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="11"/>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="14">
+    <row r="36" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -2073,30 +1720,30 @@
       <c r="I36" s="5"/>
       <c r="J36" s="11"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="5">
+      <c r="C37" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="11"/>
     </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="14">
+    <row r="38" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -2121,30 +1768,30 @@
       <c r="I38" s="5"/>
       <c r="J38" s="11"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="5">
+      <c r="C39" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="11"/>
     </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="14">
+    <row r="40" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -2169,30 +1816,30 @@
       <c r="I40" s="5"/>
       <c r="J40" s="11"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="5">
+      <c r="C41" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="11"/>
     </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="14">
+    <row r="42" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -2217,30 +1864,30 @@
       <c r="I42" s="5"/>
       <c r="J42" s="11"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="5">
+      <c r="C43" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="5" t="n">
         <v>35000</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="11"/>
     </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="14">
+    <row r="44" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -2263,19 +1910,19 @@
       <c r="I44" s="5"/>
       <c r="J44" s="11"/>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14"/>
       <c r="B45" s="12"/>
-      <c r="C45" s="13">
+      <c r="C45" s="13" t="n">
         <v>35000</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="13"/>
@@ -2283,8 +1930,8 @@
       <c r="I45" s="5"/>
       <c r="J45" s="11"/>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="14">
+    <row r="46" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -2305,16 +1952,16 @@
       <c r="I46" s="5"/>
       <c r="J46" s="11"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14"/>
       <c r="B47" s="4"/>
-      <c r="C47" s="5">
+      <c r="C47" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="5"/>
@@ -2323,8 +1970,8 @@
       <c r="I47" s="5"/>
       <c r="J47" s="11"/>
     </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="14">
+    <row r="48" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2341,10 +1988,10 @@
       <c r="I48" s="5"/>
       <c r="J48" s="11"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14"/>
       <c r="B49" s="12"/>
-      <c r="C49" s="13">
+      <c r="C49" s="13" t="n">
         <v>0.99</v>
       </c>
       <c r="D49" s="13"/>
@@ -2355,8 +2002,8 @@
       <c r="I49" s="5"/>
       <c r="J49" s="11"/>
     </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="14">
+    <row r="50" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2373,10 +2020,10 @@
       <c r="I50" s="5"/>
       <c r="J50" s="11"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="4">
+      <c r="C51" s="4" t="n">
         <v>0.999</v>
       </c>
       <c r="D51" s="5"/>
@@ -2387,7 +2034,7 @@
       <c r="I51" s="5"/>
       <c r="J51" s="11"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2399,7 +2046,7 @@
       <c r="I52" s="5"/>
       <c r="J52" s="11"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2411,7 +2058,7 @@
       <c r="I53" s="5"/>
       <c r="J53" s="11"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2423,7 +2070,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="11"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2435,7 +2082,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2447,79 +2094,43 @@
       <c r="I56" s="5"/>
       <c r="J56" s="11"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14"/>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="11"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14"/>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="11"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="14"/>
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="11"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="11"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14"/>
-      <c r="B61"/>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="11"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14"/>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="11"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2531,7 +2142,7 @@
       <c r="I63" s="5"/>
       <c r="J63" s="11"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2543,7 +2154,7 @@
       <c r="I64" s="5"/>
       <c r="J64" s="11"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2555,7 +2166,7 @@
       <c r="I65" s="5"/>
       <c r="J65" s="11"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2567,7 +2178,7 @@
       <c r="I66" s="5"/>
       <c r="J66" s="11"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2579,7 +2190,7 @@
       <c r="I67" s="5"/>
       <c r="J67" s="11"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2591,7 +2202,7 @@
       <c r="I68" s="5"/>
       <c r="J68" s="11"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2603,7 +2214,7 @@
       <c r="I69" s="5"/>
       <c r="J69" s="11"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2615,7 +2226,7 @@
       <c r="I70" s="5"/>
       <c r="J70" s="11"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2627,7 +2238,7 @@
       <c r="I71" s="5"/>
       <c r="J71" s="11"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -2639,7 +2250,7 @@
       <c r="I72" s="5"/>
       <c r="J72" s="11"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2651,7 +2262,7 @@
       <c r="I73" s="5"/>
       <c r="J73" s="11"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="14"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2663,7 +2274,7 @@
       <c r="I74" s="5"/>
       <c r="J74" s="11"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -2675,7 +2286,7 @@
       <c r="I75" s="5"/>
       <c r="J75" s="11"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -2687,7 +2298,7 @@
       <c r="I76" s="5"/>
       <c r="J76" s="11"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -2699,7 +2310,7 @@
       <c r="I77" s="5"/>
       <c r="J77" s="11"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -2711,7 +2322,7 @@
       <c r="I78" s="5"/>
       <c r="J78" s="11"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="14"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -2723,7 +2334,7 @@
       <c r="I79" s="5"/>
       <c r="J79" s="11"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -2735,7 +2346,7 @@
       <c r="I80" s="5"/>
       <c r="J80" s="11"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -2747,7 +2358,7 @@
       <c r="I81" s="5"/>
       <c r="J81" s="11"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -2759,7 +2370,7 @@
       <c r="I82" s="5"/>
       <c r="J82" s="11"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="14"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2771,7 +2382,7 @@
       <c r="I83" s="5"/>
       <c r="J83" s="11"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -2783,7 +2394,7 @@
       <c r="I84" s="5"/>
       <c r="J84" s="11"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -2795,7 +2406,7 @@
       <c r="I85" s="5"/>
       <c r="J85" s="11"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -2807,7 +2418,7 @@
       <c r="I86" s="5"/>
       <c r="J86" s="11"/>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -2819,7 +2430,7 @@
       <c r="I87" s="5"/>
       <c r="J87" s="11"/>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -2831,7 +2442,7 @@
       <c r="I88" s="5"/>
       <c r="J88" s="11"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -2843,7 +2454,7 @@
       <c r="I89" s="5"/>
       <c r="J89" s="11"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -2855,7 +2466,7 @@
       <c r="I90" s="5"/>
       <c r="J90" s="11"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -2867,7 +2478,7 @@
       <c r="I91" s="5"/>
       <c r="J91" s="11"/>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="14"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -2879,7 +2490,7 @@
       <c r="I92" s="5"/>
       <c r="J92" s="11"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -2891,7 +2502,7 @@
       <c r="I93" s="5"/>
       <c r="J93" s="11"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -2903,7 +2514,7 @@
       <c r="I94" s="5"/>
       <c r="J94" s="11"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="14"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -2915,7 +2526,7 @@
       <c r="I95" s="5"/>
       <c r="J95" s="11"/>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="14"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -2927,7 +2538,7 @@
       <c r="I96" s="5"/>
       <c r="J96" s="11"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -2939,7 +2550,7 @@
       <c r="I97" s="5"/>
       <c r="J97" s="11"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -2951,7 +2562,7 @@
       <c r="I98" s="5"/>
       <c r="J98" s="11"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -2963,7 +2574,7 @@
       <c r="I99" s="5"/>
       <c r="J99" s="11"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="14"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -2975,7 +2586,7 @@
       <c r="I100" s="5"/>
       <c r="J100" s="11"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -2987,7 +2598,7 @@
       <c r="I101" s="5"/>
       <c r="J101" s="11"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -2999,7 +2610,7 @@
       <c r="I102" s="5"/>
       <c r="J102" s="11"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="14"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -3011,7 +2622,7 @@
       <c r="I103" s="5"/>
       <c r="J103" s="11"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -3023,7 +2634,7 @@
       <c r="I104" s="5"/>
       <c r="J104" s="11"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -3035,7 +2646,7 @@
       <c r="I105" s="5"/>
       <c r="J105" s="11"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="14"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -3047,7 +2658,7 @@
       <c r="I106" s="5"/>
       <c r="J106" s="11"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="14"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -3059,7 +2670,7 @@
       <c r="I107" s="5"/>
       <c r="J107" s="11"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="14"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -3071,7 +2682,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="11"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="14"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -3083,7 +2694,7 @@
       <c r="I109" s="5"/>
       <c r="J109" s="11"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="14"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -3095,7 +2706,7 @@
       <c r="I110" s="5"/>
       <c r="J110" s="11"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="14"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -3107,7 +2718,7 @@
       <c r="I111" s="5"/>
       <c r="J111" s="11"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="14"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -3119,7 +2730,7 @@
       <c r="I112" s="5"/>
       <c r="J112" s="11"/>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="14"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -3131,7 +2742,7 @@
       <c r="I113" s="5"/>
       <c r="J113" s="11"/>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="14"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -3143,7 +2754,7 @@
       <c r="I114" s="5"/>
       <c r="J114" s="11"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="14"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -3155,7 +2766,7 @@
       <c r="I115" s="5"/>
       <c r="J115" s="11"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="14"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -3167,7 +2778,7 @@
       <c r="I116" s="5"/>
       <c r="J116" s="11"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -3179,7 +2790,7 @@
       <c r="I117" s="5"/>
       <c r="J117" s="11"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="14"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -3191,7 +2802,7 @@
       <c r="I118" s="5"/>
       <c r="J118" s="11"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="14"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -3203,7 +2814,7 @@
       <c r="I119" s="5"/>
       <c r="J119" s="11"/>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="14"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -3215,7 +2826,7 @@
       <c r="I120" s="5"/>
       <c r="J120" s="11"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="14"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -3227,7 +2838,7 @@
       <c r="I121" s="5"/>
       <c r="J121" s="11"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="14"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -3239,7 +2850,7 @@
       <c r="I122" s="5"/>
       <c r="J122" s="11"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="14"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -3251,7 +2862,7 @@
       <c r="I123" s="5"/>
       <c r="J123" s="11"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="14"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -3263,7 +2874,7 @@
       <c r="I124" s="5"/>
       <c r="J124" s="11"/>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="14"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -3275,7 +2886,7 @@
       <c r="I125" s="5"/>
       <c r="J125" s="11"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="14"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -3287,7 +2898,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="11"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="14"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -3299,7 +2910,7 @@
       <c r="I127" s="5"/>
       <c r="J127" s="11"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="14"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -3311,7 +2922,7 @@
       <c r="I128" s="5"/>
       <c r="J128" s="11"/>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="14"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -3323,7 +2934,7 @@
       <c r="I129" s="5"/>
       <c r="J129" s="11"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="14"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -3335,7 +2946,7 @@
       <c r="I130" s="5"/>
       <c r="J130" s="11"/>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="14"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -3347,7 +2958,7 @@
       <c r="I131" s="5"/>
       <c r="J131" s="11"/>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="14"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -3359,7 +2970,7 @@
       <c r="I132" s="5"/>
       <c r="J132" s="11"/>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="14"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -3371,7 +2982,7 @@
       <c r="I133" s="5"/>
       <c r="J133" s="11"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="14"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -3383,7 +2994,7 @@
       <c r="I134" s="5"/>
       <c r="J134" s="11"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="14"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -3395,7 +3006,7 @@
       <c r="I135" s="5"/>
       <c r="J135" s="11"/>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="14"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -3407,7 +3018,7 @@
       <c r="I136" s="5"/>
       <c r="J136" s="11"/>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="14"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -3419,7 +3030,7 @@
       <c r="I137" s="5"/>
       <c r="J137" s="11"/>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="14"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -3431,7 +3042,7 @@
       <c r="I138" s="5"/>
       <c r="J138" s="11"/>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="14"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -3443,7 +3054,7 @@
       <c r="I139" s="5"/>
       <c r="J139" s="11"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="14"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -3455,7 +3066,7 @@
       <c r="I140" s="5"/>
       <c r="J140" s="11"/>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="14"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -3467,7 +3078,7 @@
       <c r="I141" s="5"/>
       <c r="J141" s="11"/>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="14"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -3479,7 +3090,7 @@
       <c r="I142" s="5"/>
       <c r="J142" s="11"/>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="14"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -3491,7 +3102,7 @@
       <c r="I143" s="5"/>
       <c r="J143" s="11"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="14"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -3503,7 +3114,7 @@
       <c r="I144" s="5"/>
       <c r="J144" s="11"/>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="14"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -3515,7 +3126,7 @@
       <c r="I145" s="5"/>
       <c r="J145" s="11"/>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="14"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -3527,7 +3138,7 @@
       <c r="I146" s="5"/>
       <c r="J146" s="11"/>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="14"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -3539,7 +3150,7 @@
       <c r="I147" s="5"/>
       <c r="J147" s="11"/>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="14"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -3551,7 +3162,7 @@
       <c r="I148" s="5"/>
       <c r="J148" s="11"/>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="14"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -3563,7 +3174,7 @@
       <c r="I149" s="5"/>
       <c r="J149" s="11"/>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="14"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -3575,7 +3186,7 @@
       <c r="I150" s="5"/>
       <c r="J150" s="11"/>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="14"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -3587,7 +3198,7 @@
       <c r="I151" s="5"/>
       <c r="J151" s="11"/>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="14"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -3599,7 +3210,7 @@
       <c r="I152" s="5"/>
       <c r="J152" s="11"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="14"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -3611,7 +3222,7 @@
       <c r="I153" s="5"/>
       <c r="J153" s="11"/>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="14"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -3623,7 +3234,7 @@
       <c r="I154" s="5"/>
       <c r="J154" s="11"/>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="14"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -3635,7 +3246,7 @@
       <c r="I155" s="5"/>
       <c r="J155" s="11"/>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="14"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -3647,7 +3258,7 @@
       <c r="I156" s="5"/>
       <c r="J156" s="11"/>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="14"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -3659,7 +3270,7 @@
       <c r="I157" s="5"/>
       <c r="J157" s="11"/>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="14"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -3671,7 +3282,7 @@
       <c r="I158" s="5"/>
       <c r="J158" s="11"/>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="14"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -3683,7 +3294,7 @@
       <c r="I159" s="5"/>
       <c r="J159" s="11"/>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="14"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -3695,7 +3306,7 @@
       <c r="I160" s="5"/>
       <c r="J160" s="11"/>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="14"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -3707,7 +3318,7 @@
       <c r="I161" s="5"/>
       <c r="J161" s="11"/>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="14"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -3719,7 +3330,7 @@
       <c r="I162" s="5"/>
       <c r="J162" s="11"/>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="14"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -3731,7 +3342,7 @@
       <c r="I163" s="5"/>
       <c r="J163" s="11"/>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="14"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -3743,7 +3354,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="11"/>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="14"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -3755,7 +3366,7 @@
       <c r="I165" s="5"/>
       <c r="J165" s="11"/>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="14"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -3767,7 +3378,7 @@
       <c r="I166" s="5"/>
       <c r="J166" s="11"/>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="14"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -3779,7 +3390,7 @@
       <c r="I167" s="5"/>
       <c r="J167" s="11"/>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="14"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -3791,7 +3402,7 @@
       <c r="I168" s="5"/>
       <c r="J168" s="11"/>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="14"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -3803,7 +3414,7 @@
       <c r="I169" s="5"/>
       <c r="J169" s="11"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="14"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -3815,7 +3426,7 @@
       <c r="I170" s="5"/>
       <c r="J170" s="11"/>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="14"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -3827,7 +3438,7 @@
       <c r="I171" s="5"/>
       <c r="J171" s="11"/>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="14"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -3839,7 +3450,7 @@
       <c r="I172" s="5"/>
       <c r="J172" s="11"/>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="14"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -3851,7 +3462,7 @@
       <c r="I173" s="5"/>
       <c r="J173" s="11"/>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="14"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -3863,7 +3474,7 @@
       <c r="I174" s="5"/>
       <c r="J174" s="11"/>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="14"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -3875,7 +3486,7 @@
       <c r="I175" s="5"/>
       <c r="J175" s="11"/>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="14"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -3887,7 +3498,7 @@
       <c r="I176" s="5"/>
       <c r="J176" s="11"/>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="14"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -3899,7 +3510,7 @@
       <c r="I177" s="5"/>
       <c r="J177" s="11"/>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="14"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -3911,7 +3522,7 @@
       <c r="I178" s="5"/>
       <c r="J178" s="11"/>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="14"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -3923,7 +3534,7 @@
       <c r="I179" s="5"/>
       <c r="J179" s="11"/>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="14"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -3935,7 +3546,7 @@
       <c r="I180" s="5"/>
       <c r="J180" s="11"/>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="14"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -3947,7 +3558,7 @@
       <c r="I181" s="5"/>
       <c r="J181" s="11"/>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="14"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -3959,7 +3570,7 @@
       <c r="I182" s="5"/>
       <c r="J182" s="11"/>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="14"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -3971,7 +3582,7 @@
       <c r="I183" s="5"/>
       <c r="J183" s="11"/>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="14"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -3983,7 +3594,7 @@
       <c r="I184" s="5"/>
       <c r="J184" s="11"/>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="14"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -3995,7 +3606,7 @@
       <c r="I185" s="5"/>
       <c r="J185" s="11"/>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="14"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -4007,7 +3618,7 @@
       <c r="I186" s="5"/>
       <c r="J186" s="11"/>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="14"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -4019,7 +3630,7 @@
       <c r="I187" s="5"/>
       <c r="J187" s="11"/>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="14"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -4031,7 +3642,7 @@
       <c r="I188" s="5"/>
       <c r="J188" s="11"/>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="14"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -4043,7 +3654,7 @@
       <c r="I189" s="5"/>
       <c r="J189" s="11"/>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="14"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -4055,7 +3666,7 @@
       <c r="I190" s="5"/>
       <c r="J190" s="11"/>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="14"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -4067,7 +3678,7 @@
       <c r="I191" s="5"/>
       <c r="J191" s="11"/>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="14"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -4079,7 +3690,7 @@
       <c r="I192" s="5"/>
       <c r="J192" s="11"/>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="14"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -4091,7 +3702,7 @@
       <c r="I193" s="5"/>
       <c r="J193" s="11"/>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="14"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -4103,7 +3714,7 @@
       <c r="I194" s="5"/>
       <c r="J194" s="11"/>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="14"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -4115,7 +3726,7 @@
       <c r="I195" s="5"/>
       <c r="J195" s="11"/>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="14"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -4127,7 +3738,7 @@
       <c r="I196" s="5"/>
       <c r="J196" s="11"/>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="14"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -4139,7 +3750,7 @@
       <c r="I197" s="5"/>
       <c r="J197" s="11"/>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="14"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -4151,7 +3762,7 @@
       <c r="I198" s="5"/>
       <c r="J198" s="11"/>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="14"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -4163,7 +3774,7 @@
       <c r="I199" s="5"/>
       <c r="J199" s="11"/>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="14"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -4175,7 +3786,7 @@
       <c r="I200" s="5"/>
       <c r="J200" s="11"/>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="14"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -4187,7 +3798,7 @@
       <c r="I201" s="5"/>
       <c r="J201" s="11"/>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="14"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -4199,7 +3810,7 @@
       <c r="I202" s="5"/>
       <c r="J202" s="11"/>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="14"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -4211,7 +3822,7 @@
       <c r="I203" s="5"/>
       <c r="J203" s="11"/>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="14"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -4223,7 +3834,7 @@
       <c r="I204" s="5"/>
       <c r="J204" s="11"/>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="14"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -4235,7 +3846,7 @@
       <c r="I205" s="5"/>
       <c r="J205" s="11"/>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="14"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -4247,7 +3858,7 @@
       <c r="I206" s="5"/>
       <c r="J206" s="11"/>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="14"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -4259,7 +3870,7 @@
       <c r="I207" s="5"/>
       <c r="J207" s="11"/>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="14"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -4271,7 +3882,7 @@
       <c r="I208" s="5"/>
       <c r="J208" s="11"/>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="14"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -4283,7 +3894,7 @@
       <c r="I209" s="5"/>
       <c r="J209" s="11"/>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="14"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -4295,7 +3906,7 @@
       <c r="I210" s="5"/>
       <c r="J210" s="11"/>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="14"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -4307,7 +3918,7 @@
       <c r="I211" s="5"/>
       <c r="J211" s="11"/>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="15"/>
       <c r="B212" s="16"/>
       <c r="C212" s="16"/>
@@ -4321,64 +3932,72 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2 H2:AMJ27 C24:G29 H28:J51 A28:A52 K28:AMJ1048576 C30:D43 G30:G43 C44:G45 A52:J56 H57:J62 A63:J1048576">
-    <cfRule type="expression" dxfId="20" priority="5">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G5 C6:D19 G6:G19 C20:G21">
-    <cfRule type="expression" dxfId="18" priority="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:F19">
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:F43">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22:G23 G46:G47 C48:G51">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:AMJ1 A57:A62">
-    <cfRule type="expression" dxfId="14" priority="7">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BA2653E-7E99-4047-B201-5BD44C2A87ED}">
-  <dimension ref="A1:AMK214"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J214"/>
+  <sheetFormatPr defaultRowHeight="15.6" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.19921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.796875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" style="1" customWidth="1"/>
-    <col min="8" max="1025" width="10.796875" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="1" width="10.8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.2" thickBot="1">
+    <row r="1" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
@@ -4410,8 +4029,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7">
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -4428,10 +4047,10 @@
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="4">
+      <c r="C3" s="4" t="n">
         <v>0.995</v>
       </c>
       <c r="D3" s="5"/>
@@ -4442,8 +4061,8 @@
       <c r="I3" s="5"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="10">
+    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -4466,19 +4085,19 @@
       <c r="I4" s="5"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="13">
+      <c r="C5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="13" t="n">
         <v>0.08</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="13"/>
@@ -4486,8 +4105,8 @@
       <c r="I5" s="5"/>
       <c r="J5" s="11"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="10">
+    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -4512,30 +4131,30 @@
       <c r="I6" s="5"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="11"/>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="10">
+    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -4560,30 +4179,30 @@
       <c r="I8" s="5"/>
       <c r="J8" s="11"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="5">
+      <c r="C9" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="11"/>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="10">
+    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4608,30 +4227,30 @@
       <c r="I10" s="5"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="5">
+      <c r="C11" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="11"/>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="10">
+    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -4656,30 +4275,30 @@
       <c r="I12" s="5"/>
       <c r="J12" s="11"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="5">
+      <c r="C13" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="11"/>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="10">
+    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -4704,30 +4323,30 @@
       <c r="I14" s="5"/>
       <c r="J14" s="11"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="5">
+      <c r="C15" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="11"/>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="10">
+    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4752,30 +4371,30 @@
       <c r="I16" s="5"/>
       <c r="J16" s="11"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="5">
+      <c r="C17" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="11"/>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="10">
+    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -4800,30 +4419,30 @@
       <c r="I18" s="5"/>
       <c r="J18" s="11"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="5">
+      <c r="C19" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="5" t="n">
         <v>35000</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="11"/>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="10">
+    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="n">
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -4846,19 +4465,19 @@
       <c r="I20" s="5"/>
       <c r="J20" s="11"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
       <c r="B21" s="12"/>
-      <c r="C21" s="13">
+      <c r="C21" s="13" t="n">
         <v>35000</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="13" t="n">
         <v>0.8</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="13"/>
@@ -4866,8 +4485,8 @@
       <c r="I21" s="5"/>
       <c r="J21" s="11"/>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="10">
+    <row r="22" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="n">
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -4888,16 +4507,16 @@
       <c r="I22" s="5"/>
       <c r="J22" s="11"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="5">
+      <c r="C23" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="5"/>
@@ -4906,8 +4525,8 @@
       <c r="I23" s="5"/>
       <c r="J23" s="11"/>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="10">
+    <row r="24" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="n">
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -4924,10 +4543,10 @@
       <c r="I24" s="5"/>
       <c r="J24" s="11"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
       <c r="B25" s="12"/>
-      <c r="C25" s="13">
+      <c r="C25" s="13" t="n">
         <v>0.99</v>
       </c>
       <c r="D25" s="13"/>
@@ -4938,8 +4557,8 @@
       <c r="I25" s="5"/>
       <c r="J25" s="11"/>
     </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="10">
+    <row r="26" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="n">
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -4956,10 +4575,10 @@
       <c r="I26" s="5"/>
       <c r="J26" s="11"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="4">
+      <c r="C27" s="4" t="n">
         <v>0.999</v>
       </c>
       <c r="D27" s="5"/>
@@ -4970,8 +4589,8 @@
       <c r="I27" s="5"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="14">
+    <row r="28" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -4988,10 +4607,10 @@
       <c r="I28" s="5"/>
       <c r="J28" s="11"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14"/>
       <c r="B29" s="4"/>
-      <c r="C29" s="5">
+      <c r="C29" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D29" s="5"/>
@@ -5002,8 +4621,8 @@
       <c r="I29" s="5"/>
       <c r="J29" s="11"/>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="14">
+    <row r="30" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -5026,19 +4645,19 @@
       <c r="I30" s="5"/>
       <c r="J30" s="11"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14"/>
       <c r="B31" s="12"/>
-      <c r="C31" s="13">
+      <c r="C31" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="13" t="n">
         <v>0.08</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="13"/>
@@ -5046,8 +4665,8 @@
       <c r="I31" s="5"/>
       <c r="J31" s="11"/>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="14">
+    <row r="32" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -5072,30 +4691,30 @@
       <c r="I32" s="5"/>
       <c r="J32" s="11"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="5">
+      <c r="C33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="11"/>
     </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="14">
+    <row r="34" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -5120,30 +4739,30 @@
       <c r="I34" s="5"/>
       <c r="J34" s="11"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="5">
+      <c r="C35" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="11"/>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="14">
+    <row r="36" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -5168,30 +4787,30 @@
       <c r="I36" s="5"/>
       <c r="J36" s="11"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="5">
+      <c r="C37" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="11"/>
     </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="14">
+    <row r="38" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -5216,30 +4835,30 @@
       <c r="I38" s="5"/>
       <c r="J38" s="11"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="5">
+      <c r="C39" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="11"/>
     </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="14">
+    <row r="40" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -5264,30 +4883,30 @@
       <c r="I40" s="5"/>
       <c r="J40" s="11"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="5">
+      <c r="C41" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="11"/>
     </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="14">
+    <row r="42" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -5312,30 +4931,30 @@
       <c r="I42" s="5"/>
       <c r="J42" s="11"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="5">
+      <c r="C43" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="11"/>
     </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="14">
+    <row r="44" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -5360,30 +4979,30 @@
       <c r="I44" s="5"/>
       <c r="J44" s="11"/>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="5">
+      <c r="C45" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="5" t="n">
         <v>35000</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="11"/>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="14">
+    <row r="46" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -5406,19 +5025,19 @@
       <c r="I46" s="5"/>
       <c r="J46" s="11"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14"/>
       <c r="B47" s="12"/>
-      <c r="C47" s="13">
+      <c r="C47" s="13" t="n">
         <v>35000</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="13" t="n">
         <v>0.8</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="13"/>
@@ -5426,8 +5045,8 @@
       <c r="I47" s="5"/>
       <c r="J47" s="11"/>
     </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="14">
+    <row r="48" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="n">
         <v>24</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -5448,16 +5067,16 @@
       <c r="I48" s="5"/>
       <c r="J48" s="11"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14"/>
       <c r="B49" s="4"/>
-      <c r="C49" s="5">
+      <c r="C49" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="5"/>
@@ -5466,8 +5085,8 @@
       <c r="I49" s="5"/>
       <c r="J49" s="11"/>
     </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="14">
+    <row r="50" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="n">
         <v>25</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -5484,10 +5103,10 @@
       <c r="I50" s="5"/>
       <c r="J50" s="11"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14"/>
       <c r="B51" s="12"/>
-      <c r="C51" s="13">
+      <c r="C51" s="13" t="n">
         <v>0.99</v>
       </c>
       <c r="D51" s="13"/>
@@ -5498,8 +5117,8 @@
       <c r="I51" s="5"/>
       <c r="J51" s="11"/>
     </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="14">
+    <row r="52" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14" t="n">
         <v>26</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -5516,10 +5135,10 @@
       <c r="I52" s="5"/>
       <c r="J52" s="11"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="4">
+      <c r="C53" s="4" t="n">
         <v>0.999</v>
       </c>
       <c r="D53" s="5"/>
@@ -5530,7 +5149,7 @@
       <c r="I53" s="5"/>
       <c r="J53" s="11"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -5542,7 +5161,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="11"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -5554,7 +5173,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -5566,7 +5185,7 @@
       <c r="I56" s="5"/>
       <c r="J56" s="11"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -5578,7 +5197,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="11"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -5590,79 +5209,43 @@
       <c r="I58" s="5"/>
       <c r="J58" s="11"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="14"/>
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="11"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="11"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14"/>
-      <c r="B61"/>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="11"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14"/>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="11"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14"/>
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="11"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14"/>
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="11"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -5674,7 +5257,7 @@
       <c r="I65" s="5"/>
       <c r="J65" s="11"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -5686,7 +5269,7 @@
       <c r="I66" s="5"/>
       <c r="J66" s="11"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -5698,7 +5281,7 @@
       <c r="I67" s="5"/>
       <c r="J67" s="11"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -5710,7 +5293,7 @@
       <c r="I68" s="5"/>
       <c r="J68" s="11"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -5722,7 +5305,7 @@
       <c r="I69" s="5"/>
       <c r="J69" s="11"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -5734,7 +5317,7 @@
       <c r="I70" s="5"/>
       <c r="J70" s="11"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -5746,7 +5329,7 @@
       <c r="I71" s="5"/>
       <c r="J71" s="11"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -5758,7 +5341,7 @@
       <c r="I72" s="5"/>
       <c r="J72" s="11"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -5770,7 +5353,7 @@
       <c r="I73" s="5"/>
       <c r="J73" s="11"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="14"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -5782,7 +5365,7 @@
       <c r="I74" s="5"/>
       <c r="J74" s="11"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -5794,7 +5377,7 @@
       <c r="I75" s="5"/>
       <c r="J75" s="11"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -5806,7 +5389,7 @@
       <c r="I76" s="5"/>
       <c r="J76" s="11"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -5818,7 +5401,7 @@
       <c r="I77" s="5"/>
       <c r="J77" s="11"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -5830,7 +5413,7 @@
       <c r="I78" s="5"/>
       <c r="J78" s="11"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="14"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -5842,7 +5425,7 @@
       <c r="I79" s="5"/>
       <c r="J79" s="11"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -5854,7 +5437,7 @@
       <c r="I80" s="5"/>
       <c r="J80" s="11"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -5866,7 +5449,7 @@
       <c r="I81" s="5"/>
       <c r="J81" s="11"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -5878,7 +5461,7 @@
       <c r="I82" s="5"/>
       <c r="J82" s="11"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="14"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -5890,7 +5473,7 @@
       <c r="I83" s="5"/>
       <c r="J83" s="11"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -5902,7 +5485,7 @@
       <c r="I84" s="5"/>
       <c r="J84" s="11"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -5914,7 +5497,7 @@
       <c r="I85" s="5"/>
       <c r="J85" s="11"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -5926,7 +5509,7 @@
       <c r="I86" s="5"/>
       <c r="J86" s="11"/>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -5938,7 +5521,7 @@
       <c r="I87" s="5"/>
       <c r="J87" s="11"/>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -5950,7 +5533,7 @@
       <c r="I88" s="5"/>
       <c r="J88" s="11"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -5962,7 +5545,7 @@
       <c r="I89" s="5"/>
       <c r="J89" s="11"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -5974,7 +5557,7 @@
       <c r="I90" s="5"/>
       <c r="J90" s="11"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -5986,7 +5569,7 @@
       <c r="I91" s="5"/>
       <c r="J91" s="11"/>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="14"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -5998,7 +5581,7 @@
       <c r="I92" s="5"/>
       <c r="J92" s="11"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -6010,7 +5593,7 @@
       <c r="I93" s="5"/>
       <c r="J93" s="11"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -6022,7 +5605,7 @@
       <c r="I94" s="5"/>
       <c r="J94" s="11"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="14"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -6034,7 +5617,7 @@
       <c r="I95" s="5"/>
       <c r="J95" s="11"/>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="14"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -6046,7 +5629,7 @@
       <c r="I96" s="5"/>
       <c r="J96" s="11"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -6058,7 +5641,7 @@
       <c r="I97" s="5"/>
       <c r="J97" s="11"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -6070,7 +5653,7 @@
       <c r="I98" s="5"/>
       <c r="J98" s="11"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -6082,7 +5665,7 @@
       <c r="I99" s="5"/>
       <c r="J99" s="11"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="14"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -6094,7 +5677,7 @@
       <c r="I100" s="5"/>
       <c r="J100" s="11"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -6106,7 +5689,7 @@
       <c r="I101" s="5"/>
       <c r="J101" s="11"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -6118,7 +5701,7 @@
       <c r="I102" s="5"/>
       <c r="J102" s="11"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="14"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -6130,7 +5713,7 @@
       <c r="I103" s="5"/>
       <c r="J103" s="11"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -6142,7 +5725,7 @@
       <c r="I104" s="5"/>
       <c r="J104" s="11"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -6154,7 +5737,7 @@
       <c r="I105" s="5"/>
       <c r="J105" s="11"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="14"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -6166,7 +5749,7 @@
       <c r="I106" s="5"/>
       <c r="J106" s="11"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="14"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -6178,7 +5761,7 @@
       <c r="I107" s="5"/>
       <c r="J107" s="11"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="14"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -6190,7 +5773,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="11"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="14"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -6202,7 +5785,7 @@
       <c r="I109" s="5"/>
       <c r="J109" s="11"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="14"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -6214,7 +5797,7 @@
       <c r="I110" s="5"/>
       <c r="J110" s="11"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="14"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -6226,7 +5809,7 @@
       <c r="I111" s="5"/>
       <c r="J111" s="11"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="14"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -6238,7 +5821,7 @@
       <c r="I112" s="5"/>
       <c r="J112" s="11"/>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="14"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -6250,7 +5833,7 @@
       <c r="I113" s="5"/>
       <c r="J113" s="11"/>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="14"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -6262,7 +5845,7 @@
       <c r="I114" s="5"/>
       <c r="J114" s="11"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="14"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -6274,7 +5857,7 @@
       <c r="I115" s="5"/>
       <c r="J115" s="11"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="14"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -6286,7 +5869,7 @@
       <c r="I116" s="5"/>
       <c r="J116" s="11"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -6298,7 +5881,7 @@
       <c r="I117" s="5"/>
       <c r="J117" s="11"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="14"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -6310,7 +5893,7 @@
       <c r="I118" s="5"/>
       <c r="J118" s="11"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="14"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -6322,7 +5905,7 @@
       <c r="I119" s="5"/>
       <c r="J119" s="11"/>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="14"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -6334,7 +5917,7 @@
       <c r="I120" s="5"/>
       <c r="J120" s="11"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="14"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -6346,7 +5929,7 @@
       <c r="I121" s="5"/>
       <c r="J121" s="11"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="14"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -6358,7 +5941,7 @@
       <c r="I122" s="5"/>
       <c r="J122" s="11"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="14"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -6370,7 +5953,7 @@
       <c r="I123" s="5"/>
       <c r="J123" s="11"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="14"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -6382,7 +5965,7 @@
       <c r="I124" s="5"/>
       <c r="J124" s="11"/>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="14"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -6394,7 +5977,7 @@
       <c r="I125" s="5"/>
       <c r="J125" s="11"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="14"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -6406,7 +5989,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="11"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="14"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -6418,7 +6001,7 @@
       <c r="I127" s="5"/>
       <c r="J127" s="11"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="14"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -6430,7 +6013,7 @@
       <c r="I128" s="5"/>
       <c r="J128" s="11"/>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="14"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -6442,7 +6025,7 @@
       <c r="I129" s="5"/>
       <c r="J129" s="11"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="14"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -6454,7 +6037,7 @@
       <c r="I130" s="5"/>
       <c r="J130" s="11"/>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="14"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -6466,7 +6049,7 @@
       <c r="I131" s="5"/>
       <c r="J131" s="11"/>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="14"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -6478,7 +6061,7 @@
       <c r="I132" s="5"/>
       <c r="J132" s="11"/>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="14"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -6490,7 +6073,7 @@
       <c r="I133" s="5"/>
       <c r="J133" s="11"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="14"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -6502,7 +6085,7 @@
       <c r="I134" s="5"/>
       <c r="J134" s="11"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="14"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -6514,7 +6097,7 @@
       <c r="I135" s="5"/>
       <c r="J135" s="11"/>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="14"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -6526,7 +6109,7 @@
       <c r="I136" s="5"/>
       <c r="J136" s="11"/>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="14"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -6538,7 +6121,7 @@
       <c r="I137" s="5"/>
       <c r="J137" s="11"/>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="14"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -6550,7 +6133,7 @@
       <c r="I138" s="5"/>
       <c r="J138" s="11"/>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="14"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -6562,7 +6145,7 @@
       <c r="I139" s="5"/>
       <c r="J139" s="11"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="14"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -6574,7 +6157,7 @@
       <c r="I140" s="5"/>
       <c r="J140" s="11"/>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="14"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -6586,7 +6169,7 @@
       <c r="I141" s="5"/>
       <c r="J141" s="11"/>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="14"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -6598,7 +6181,7 @@
       <c r="I142" s="5"/>
       <c r="J142" s="11"/>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="14"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -6610,7 +6193,7 @@
       <c r="I143" s="5"/>
       <c r="J143" s="11"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="14"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -6622,7 +6205,7 @@
       <c r="I144" s="5"/>
       <c r="J144" s="11"/>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="14"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -6634,7 +6217,7 @@
       <c r="I145" s="5"/>
       <c r="J145" s="11"/>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="14"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -6646,7 +6229,7 @@
       <c r="I146" s="5"/>
       <c r="J146" s="11"/>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="14"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -6658,7 +6241,7 @@
       <c r="I147" s="5"/>
       <c r="J147" s="11"/>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="14"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -6670,7 +6253,7 @@
       <c r="I148" s="5"/>
       <c r="J148" s="11"/>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="14"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -6682,7 +6265,7 @@
       <c r="I149" s="5"/>
       <c r="J149" s="11"/>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="14"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -6694,7 +6277,7 @@
       <c r="I150" s="5"/>
       <c r="J150" s="11"/>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="14"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -6706,7 +6289,7 @@
       <c r="I151" s="5"/>
       <c r="J151" s="11"/>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="14"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -6718,7 +6301,7 @@
       <c r="I152" s="5"/>
       <c r="J152" s="11"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="14"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -6730,7 +6313,7 @@
       <c r="I153" s="5"/>
       <c r="J153" s="11"/>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="14"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -6742,7 +6325,7 @@
       <c r="I154" s="5"/>
       <c r="J154" s="11"/>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="14"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -6754,7 +6337,7 @@
       <c r="I155" s="5"/>
       <c r="J155" s="11"/>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="14"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -6766,7 +6349,7 @@
       <c r="I156" s="5"/>
       <c r="J156" s="11"/>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="14"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -6778,7 +6361,7 @@
       <c r="I157" s="5"/>
       <c r="J157" s="11"/>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="14"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -6790,7 +6373,7 @@
       <c r="I158" s="5"/>
       <c r="J158" s="11"/>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="14"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -6802,7 +6385,7 @@
       <c r="I159" s="5"/>
       <c r="J159" s="11"/>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="14"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -6814,7 +6397,7 @@
       <c r="I160" s="5"/>
       <c r="J160" s="11"/>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="14"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -6826,7 +6409,7 @@
       <c r="I161" s="5"/>
       <c r="J161" s="11"/>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="14"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -6838,7 +6421,7 @@
       <c r="I162" s="5"/>
       <c r="J162" s="11"/>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="14"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -6850,7 +6433,7 @@
       <c r="I163" s="5"/>
       <c r="J163" s="11"/>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="14"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -6862,7 +6445,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="11"/>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="14"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -6874,7 +6457,7 @@
       <c r="I165" s="5"/>
       <c r="J165" s="11"/>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="14"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -6886,7 +6469,7 @@
       <c r="I166" s="5"/>
       <c r="J166" s="11"/>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="14"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -6898,7 +6481,7 @@
       <c r="I167" s="5"/>
       <c r="J167" s="11"/>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="14"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -6910,7 +6493,7 @@
       <c r="I168" s="5"/>
       <c r="J168" s="11"/>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="14"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -6922,7 +6505,7 @@
       <c r="I169" s="5"/>
       <c r="J169" s="11"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="14"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -6934,7 +6517,7 @@
       <c r="I170" s="5"/>
       <c r="J170" s="11"/>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="14"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -6946,7 +6529,7 @@
       <c r="I171" s="5"/>
       <c r="J171" s="11"/>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="14"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -6958,7 +6541,7 @@
       <c r="I172" s="5"/>
       <c r="J172" s="11"/>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="14"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -6970,7 +6553,7 @@
       <c r="I173" s="5"/>
       <c r="J173" s="11"/>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="14"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -6982,7 +6565,7 @@
       <c r="I174" s="5"/>
       <c r="J174" s="11"/>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="14"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -6994,7 +6577,7 @@
       <c r="I175" s="5"/>
       <c r="J175" s="11"/>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="14"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -7006,7 +6589,7 @@
       <c r="I176" s="5"/>
       <c r="J176" s="11"/>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="14"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -7018,7 +6601,7 @@
       <c r="I177" s="5"/>
       <c r="J177" s="11"/>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="14"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -7030,7 +6613,7 @@
       <c r="I178" s="5"/>
       <c r="J178" s="11"/>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="14"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -7042,7 +6625,7 @@
       <c r="I179" s="5"/>
       <c r="J179" s="11"/>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="14"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -7054,7 +6637,7 @@
       <c r="I180" s="5"/>
       <c r="J180" s="11"/>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="14"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -7066,7 +6649,7 @@
       <c r="I181" s="5"/>
       <c r="J181" s="11"/>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="14"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -7078,7 +6661,7 @@
       <c r="I182" s="5"/>
       <c r="J182" s="11"/>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="14"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -7090,7 +6673,7 @@
       <c r="I183" s="5"/>
       <c r="J183" s="11"/>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="14"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -7102,7 +6685,7 @@
       <c r="I184" s="5"/>
       <c r="J184" s="11"/>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="14"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -7114,7 +6697,7 @@
       <c r="I185" s="5"/>
       <c r="J185" s="11"/>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="14"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -7126,7 +6709,7 @@
       <c r="I186" s="5"/>
       <c r="J186" s="11"/>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="14"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -7138,7 +6721,7 @@
       <c r="I187" s="5"/>
       <c r="J187" s="11"/>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="14"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -7150,7 +6733,7 @@
       <c r="I188" s="5"/>
       <c r="J188" s="11"/>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="14"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -7162,7 +6745,7 @@
       <c r="I189" s="5"/>
       <c r="J189" s="11"/>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="14"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -7174,7 +6757,7 @@
       <c r="I190" s="5"/>
       <c r="J190" s="11"/>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="14"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -7186,7 +6769,7 @@
       <c r="I191" s="5"/>
       <c r="J191" s="11"/>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="14"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -7198,7 +6781,7 @@
       <c r="I192" s="5"/>
       <c r="J192" s="11"/>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="14"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -7210,7 +6793,7 @@
       <c r="I193" s="5"/>
       <c r="J193" s="11"/>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="14"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -7222,7 +6805,7 @@
       <c r="I194" s="5"/>
       <c r="J194" s="11"/>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="14"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -7234,7 +6817,7 @@
       <c r="I195" s="5"/>
       <c r="J195" s="11"/>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="14"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -7246,7 +6829,7 @@
       <c r="I196" s="5"/>
       <c r="J196" s="11"/>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="14"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -7258,7 +6841,7 @@
       <c r="I197" s="5"/>
       <c r="J197" s="11"/>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="14"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -7270,7 +6853,7 @@
       <c r="I198" s="5"/>
       <c r="J198" s="11"/>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="14"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -7282,7 +6865,7 @@
       <c r="I199" s="5"/>
       <c r="J199" s="11"/>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="14"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -7294,7 +6877,7 @@
       <c r="I200" s="5"/>
       <c r="J200" s="11"/>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="14"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -7306,7 +6889,7 @@
       <c r="I201" s="5"/>
       <c r="J201" s="11"/>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="14"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -7318,7 +6901,7 @@
       <c r="I202" s="5"/>
       <c r="J202" s="11"/>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="14"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -7330,7 +6913,7 @@
       <c r="I203" s="5"/>
       <c r="J203" s="11"/>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="14"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -7342,7 +6925,7 @@
       <c r="I204" s="5"/>
       <c r="J204" s="11"/>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="14"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -7354,7 +6937,7 @@
       <c r="I205" s="5"/>
       <c r="J205" s="11"/>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="14"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -7366,7 +6949,7 @@
       <c r="I206" s="5"/>
       <c r="J206" s="11"/>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="14"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -7378,7 +6961,7 @@
       <c r="I207" s="5"/>
       <c r="J207" s="11"/>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="14"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -7390,7 +6973,7 @@
       <c r="I208" s="5"/>
       <c r="J208" s="11"/>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="14"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -7402,7 +6985,7 @@
       <c r="I209" s="5"/>
       <c r="J209" s="11"/>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="14"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -7414,7 +6997,7 @@
       <c r="I210" s="5"/>
       <c r="J210" s="11"/>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="14"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -7426,7 +7009,7 @@
       <c r="I211" s="5"/>
       <c r="J211" s="11"/>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="14"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -7438,7 +7021,7 @@
       <c r="I212" s="5"/>
       <c r="J212" s="11"/>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="14"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -7450,7 +7033,7 @@
       <c r="I213" s="5"/>
       <c r="J213" s="11"/>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="15"/>
       <c r="B214" s="16"/>
       <c r="C214" s="16"/>
@@ -7464,62 +7047,70 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2 H2:AMJ27 C24:G31 A28:A53 H28:J53 K28:AMJ1048576 C32:D45 G32:G45 C46:G47 A54:J58 H59:J64 A65:J1048576">
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G5 C6:D19 G6:G19 C20:G21">
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:F19">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:F45">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22:G23 G48:G49 C50:G53">
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:AMJ1 A59:A64">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AMK200"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J200"/>
+  <sheetFormatPr defaultRowHeight="15.6" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.19921875" style="1" customWidth="1"/>
-    <col min="6" max="1025" width="10.796875" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="1" width="10.8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
@@ -7551,8 +7142,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7">
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -7575,28 +7166,28 @@
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="5">
+      <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="F3" s="5">
-        <v>1.5E-3</v>
+      <c r="F3" s="5" t="n">
+        <v>0.0015</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="10">
+    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -7621,30 +7212,30 @@
       <c r="I4" s="5"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="11"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="10">
+    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -7669,30 +7260,30 @@
       <c r="I6" s="5"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="5" t="n">
         <v>0.18</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="11"/>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="10">
+    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -7715,19 +7306,19 @@
       <c r="I8" s="5"/>
       <c r="J8" s="11"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="5">
+      <c r="C9" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>0.18</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5"/>
@@ -7735,8 +7326,8 @@
       <c r="I9" s="5"/>
       <c r="J9" s="11"/>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="10">
+    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -7759,19 +7350,19 @@
       <c r="I10" s="5"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="18">
+      <c r="C11" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>0.18</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5"/>
@@ -7779,8 +7370,8 @@
       <c r="I11" s="5"/>
       <c r="J11" s="11"/>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="10">
+    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -7801,17 +7392,17 @@
       <c r="I12" s="5"/>
       <c r="J12" s="11"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="18">
+      <c r="C13" s="18" t="n">
         <v>8000</v>
       </c>
-      <c r="D13" s="19">
-        <f>10/60</f>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="19" t="n">
+        <f aca="false">10/60</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="5"/>
@@ -7820,8 +7411,8 @@
       <c r="I13" s="5"/>
       <c r="J13" s="11"/>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="10">
+    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -7838,10 +7429,10 @@
       <c r="I14" s="5"/>
       <c r="J14" s="11"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="5">
+      <c r="C15" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="D15" s="5"/>
@@ -7852,8 +7443,8 @@
       <c r="I15" s="5"/>
       <c r="J15" s="11"/>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="10">
+    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -7870,11 +7461,11 @@
       <c r="I16" s="5"/>
       <c r="J16" s="11"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="5">
-        <v>1E-4</v>
+      <c r="C17" s="5" t="n">
+        <v>0.0001</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -7884,7 +7475,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="11"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -7896,7 +7487,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="11"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -7908,7 +7499,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="11"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -7920,7 +7511,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="11"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -7932,7 +7523,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="11"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -7944,7 +7535,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="11"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -7956,7 +7547,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="11"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -7968,7 +7559,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="11"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -7980,7 +7571,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="11"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -7992,7 +7583,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="11"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -8004,7 +7595,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -8016,7 +7607,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="11"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -8028,7 +7619,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="11"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -8040,7 +7631,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="11"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -8052,7 +7643,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="11"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -8064,7 +7655,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="11"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -8076,7 +7667,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="11"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -8088,7 +7679,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="11"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -8100,7 +7691,7 @@
       <c r="I35" s="5"/>
       <c r="J35" s="11"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -8112,7 +7703,7 @@
       <c r="I36" s="5"/>
       <c r="J36" s="11"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -8124,7 +7715,7 @@
       <c r="I37" s="5"/>
       <c r="J37" s="11"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -8136,7 +7727,7 @@
       <c r="I38" s="5"/>
       <c r="J38" s="11"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -8148,7 +7739,7 @@
       <c r="I39" s="5"/>
       <c r="J39" s="11"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -8160,7 +7751,7 @@
       <c r="I40" s="5"/>
       <c r="J40" s="11"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -8172,7 +7763,7 @@
       <c r="I41" s="5"/>
       <c r="J41" s="11"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -8184,7 +7775,7 @@
       <c r="I42" s="5"/>
       <c r="J42" s="11"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -8196,7 +7787,7 @@
       <c r="I43" s="5"/>
       <c r="J43" s="11"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -8208,7 +7799,7 @@
       <c r="I44" s="5"/>
       <c r="J44" s="11"/>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -8220,7 +7811,7 @@
       <c r="I45" s="5"/>
       <c r="J45" s="11"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -8232,7 +7823,7 @@
       <c r="I46" s="5"/>
       <c r="J46" s="11"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -8244,7 +7835,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="11"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -8256,7 +7847,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="11"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -8268,7 +7859,7 @@
       <c r="I49" s="5"/>
       <c r="J49" s="11"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -8280,7 +7871,7 @@
       <c r="I50" s="5"/>
       <c r="J50" s="11"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -8292,7 +7883,7 @@
       <c r="I51" s="5"/>
       <c r="J51" s="11"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -8304,7 +7895,7 @@
       <c r="I52" s="5"/>
       <c r="J52" s="11"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -8316,7 +7907,7 @@
       <c r="I53" s="5"/>
       <c r="J53" s="11"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -8328,7 +7919,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="11"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -8340,7 +7931,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -8352,7 +7943,7 @@
       <c r="I56" s="5"/>
       <c r="J56" s="11"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -8364,7 +7955,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="11"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -8376,7 +7967,7 @@
       <c r="I58" s="5"/>
       <c r="J58" s="11"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="14"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -8388,7 +7979,7 @@
       <c r="I59" s="5"/>
       <c r="J59" s="11"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -8400,7 +7991,7 @@
       <c r="I60" s="5"/>
       <c r="J60" s="11"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -8412,7 +8003,7 @@
       <c r="I61" s="5"/>
       <c r="J61" s="11"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -8424,7 +8015,7 @@
       <c r="I62" s="5"/>
       <c r="J62" s="11"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -8436,7 +8027,7 @@
       <c r="I63" s="5"/>
       <c r="J63" s="11"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -8448,7 +8039,7 @@
       <c r="I64" s="5"/>
       <c r="J64" s="11"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -8460,7 +8051,7 @@
       <c r="I65" s="5"/>
       <c r="J65" s="11"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -8472,7 +8063,7 @@
       <c r="I66" s="5"/>
       <c r="J66" s="11"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -8484,7 +8075,7 @@
       <c r="I67" s="5"/>
       <c r="J67" s="11"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -8496,7 +8087,7 @@
       <c r="I68" s="5"/>
       <c r="J68" s="11"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -8508,7 +8099,7 @@
       <c r="I69" s="5"/>
       <c r="J69" s="11"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -8520,7 +8111,7 @@
       <c r="I70" s="5"/>
       <c r="J70" s="11"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -8532,7 +8123,7 @@
       <c r="I71" s="5"/>
       <c r="J71" s="11"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -8544,7 +8135,7 @@
       <c r="I72" s="5"/>
       <c r="J72" s="11"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -8556,7 +8147,7 @@
       <c r="I73" s="5"/>
       <c r="J73" s="11"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="14"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -8568,7 +8159,7 @@
       <c r="I74" s="5"/>
       <c r="J74" s="11"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -8580,7 +8171,7 @@
       <c r="I75" s="5"/>
       <c r="J75" s="11"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -8592,7 +8183,7 @@
       <c r="I76" s="5"/>
       <c r="J76" s="11"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -8604,7 +8195,7 @@
       <c r="I77" s="5"/>
       <c r="J77" s="11"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -8616,7 +8207,7 @@
       <c r="I78" s="5"/>
       <c r="J78" s="11"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="14"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -8628,7 +8219,7 @@
       <c r="I79" s="5"/>
       <c r="J79" s="11"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -8640,7 +8231,7 @@
       <c r="I80" s="5"/>
       <c r="J80" s="11"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -8652,7 +8243,7 @@
       <c r="I81" s="5"/>
       <c r="J81" s="11"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -8664,7 +8255,7 @@
       <c r="I82" s="5"/>
       <c r="J82" s="11"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="14"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -8676,7 +8267,7 @@
       <c r="I83" s="5"/>
       <c r="J83" s="11"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -8688,7 +8279,7 @@
       <c r="I84" s="5"/>
       <c r="J84" s="11"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -8700,7 +8291,7 @@
       <c r="I85" s="5"/>
       <c r="J85" s="11"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -8712,7 +8303,7 @@
       <c r="I86" s="5"/>
       <c r="J86" s="11"/>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -8724,7 +8315,7 @@
       <c r="I87" s="5"/>
       <c r="J87" s="11"/>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -8736,7 +8327,7 @@
       <c r="I88" s="5"/>
       <c r="J88" s="11"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -8748,7 +8339,7 @@
       <c r="I89" s="5"/>
       <c r="J89" s="11"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -8760,7 +8351,7 @@
       <c r="I90" s="5"/>
       <c r="J90" s="11"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -8772,7 +8363,7 @@
       <c r="I91" s="5"/>
       <c r="J91" s="11"/>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="14"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -8784,7 +8375,7 @@
       <c r="I92" s="5"/>
       <c r="J92" s="11"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -8796,7 +8387,7 @@
       <c r="I93" s="5"/>
       <c r="J93" s="11"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -8808,7 +8399,7 @@
       <c r="I94" s="5"/>
       <c r="J94" s="11"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="14"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -8820,7 +8411,7 @@
       <c r="I95" s="5"/>
       <c r="J95" s="11"/>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="14"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -8832,7 +8423,7 @@
       <c r="I96" s="5"/>
       <c r="J96" s="11"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -8844,7 +8435,7 @@
       <c r="I97" s="5"/>
       <c r="J97" s="11"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -8856,7 +8447,7 @@
       <c r="I98" s="5"/>
       <c r="J98" s="11"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -8868,7 +8459,7 @@
       <c r="I99" s="5"/>
       <c r="J99" s="11"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="14"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -8880,7 +8471,7 @@
       <c r="I100" s="5"/>
       <c r="J100" s="11"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -8892,7 +8483,7 @@
       <c r="I101" s="5"/>
       <c r="J101" s="11"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -8904,7 +8495,7 @@
       <c r="I102" s="5"/>
       <c r="J102" s="11"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="14"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -8916,7 +8507,7 @@
       <c r="I103" s="5"/>
       <c r="J103" s="11"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -8928,7 +8519,7 @@
       <c r="I104" s="5"/>
       <c r="J104" s="11"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -8940,7 +8531,7 @@
       <c r="I105" s="5"/>
       <c r="J105" s="11"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="14"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -8952,7 +8543,7 @@
       <c r="I106" s="5"/>
       <c r="J106" s="11"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="14"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -8964,7 +8555,7 @@
       <c r="I107" s="5"/>
       <c r="J107" s="11"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="14"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -8976,7 +8567,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="11"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="14"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -8988,7 +8579,7 @@
       <c r="I109" s="5"/>
       <c r="J109" s="11"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="14"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -9000,7 +8591,7 @@
       <c r="I110" s="5"/>
       <c r="J110" s="11"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="14"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -9012,7 +8603,7 @@
       <c r="I111" s="5"/>
       <c r="J111" s="11"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="14"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -9024,7 +8615,7 @@
       <c r="I112" s="5"/>
       <c r="J112" s="11"/>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="14"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -9036,7 +8627,7 @@
       <c r="I113" s="5"/>
       <c r="J113" s="11"/>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="14"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -9048,7 +8639,7 @@
       <c r="I114" s="5"/>
       <c r="J114" s="11"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="14"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -9060,7 +8651,7 @@
       <c r="I115" s="5"/>
       <c r="J115" s="11"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="14"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -9072,7 +8663,7 @@
       <c r="I116" s="5"/>
       <c r="J116" s="11"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -9084,7 +8675,7 @@
       <c r="I117" s="5"/>
       <c r="J117" s="11"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="14"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -9096,7 +8687,7 @@
       <c r="I118" s="5"/>
       <c r="J118" s="11"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="14"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -9108,7 +8699,7 @@
       <c r="I119" s="5"/>
       <c r="J119" s="11"/>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="14"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -9120,7 +8711,7 @@
       <c r="I120" s="5"/>
       <c r="J120" s="11"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="14"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -9132,7 +8723,7 @@
       <c r="I121" s="5"/>
       <c r="J121" s="11"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="14"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -9144,7 +8735,7 @@
       <c r="I122" s="5"/>
       <c r="J122" s="11"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="14"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -9156,7 +8747,7 @@
       <c r="I123" s="5"/>
       <c r="J123" s="11"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="14"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -9168,7 +8759,7 @@
       <c r="I124" s="5"/>
       <c r="J124" s="11"/>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="14"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -9180,7 +8771,7 @@
       <c r="I125" s="5"/>
       <c r="J125" s="11"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="14"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -9192,7 +8783,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="11"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="14"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -9204,7 +8795,7 @@
       <c r="I127" s="5"/>
       <c r="J127" s="11"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="14"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -9216,7 +8807,7 @@
       <c r="I128" s="5"/>
       <c r="J128" s="11"/>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="14"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -9228,7 +8819,7 @@
       <c r="I129" s="5"/>
       <c r="J129" s="11"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="14"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -9240,7 +8831,7 @@
       <c r="I130" s="5"/>
       <c r="J130" s="11"/>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="14"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -9252,7 +8843,7 @@
       <c r="I131" s="5"/>
       <c r="J131" s="11"/>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="14"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -9264,7 +8855,7 @@
       <c r="I132" s="5"/>
       <c r="J132" s="11"/>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="14"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -9276,7 +8867,7 @@
       <c r="I133" s="5"/>
       <c r="J133" s="11"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="14"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -9288,7 +8879,7 @@
       <c r="I134" s="5"/>
       <c r="J134" s="11"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="14"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -9300,7 +8891,7 @@
       <c r="I135" s="5"/>
       <c r="J135" s="11"/>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="14"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -9312,7 +8903,7 @@
       <c r="I136" s="5"/>
       <c r="J136" s="11"/>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="14"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -9324,7 +8915,7 @@
       <c r="I137" s="5"/>
       <c r="J137" s="11"/>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="14"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -9336,7 +8927,7 @@
       <c r="I138" s="5"/>
       <c r="J138" s="11"/>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="14"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -9348,7 +8939,7 @@
       <c r="I139" s="5"/>
       <c r="J139" s="11"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="14"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -9360,7 +8951,7 @@
       <c r="I140" s="5"/>
       <c r="J140" s="11"/>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="14"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -9372,7 +8963,7 @@
       <c r="I141" s="5"/>
       <c r="J141" s="11"/>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="14"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -9384,7 +8975,7 @@
       <c r="I142" s="5"/>
       <c r="J142" s="11"/>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="14"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -9396,7 +8987,7 @@
       <c r="I143" s="5"/>
       <c r="J143" s="11"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="14"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -9408,7 +8999,7 @@
       <c r="I144" s="5"/>
       <c r="J144" s="11"/>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="14"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -9420,7 +9011,7 @@
       <c r="I145" s="5"/>
       <c r="J145" s="11"/>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="14"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -9432,7 +9023,7 @@
       <c r="I146" s="5"/>
       <c r="J146" s="11"/>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="14"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -9444,7 +9035,7 @@
       <c r="I147" s="5"/>
       <c r="J147" s="11"/>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="14"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -9456,7 +9047,7 @@
       <c r="I148" s="5"/>
       <c r="J148" s="11"/>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="14"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -9468,7 +9059,7 @@
       <c r="I149" s="5"/>
       <c r="J149" s="11"/>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="14"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -9480,7 +9071,7 @@
       <c r="I150" s="5"/>
       <c r="J150" s="11"/>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="14"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -9492,7 +9083,7 @@
       <c r="I151" s="5"/>
       <c r="J151" s="11"/>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="14"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -9504,7 +9095,7 @@
       <c r="I152" s="5"/>
       <c r="J152" s="11"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="14"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -9516,7 +9107,7 @@
       <c r="I153" s="5"/>
       <c r="J153" s="11"/>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="14"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -9528,7 +9119,7 @@
       <c r="I154" s="5"/>
       <c r="J154" s="11"/>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="14"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -9540,7 +9131,7 @@
       <c r="I155" s="5"/>
       <c r="J155" s="11"/>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="14"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -9552,7 +9143,7 @@
       <c r="I156" s="5"/>
       <c r="J156" s="11"/>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="14"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -9564,7 +9155,7 @@
       <c r="I157" s="5"/>
       <c r="J157" s="11"/>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="14"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -9576,7 +9167,7 @@
       <c r="I158" s="5"/>
       <c r="J158" s="11"/>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="14"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -9588,7 +9179,7 @@
       <c r="I159" s="5"/>
       <c r="J159" s="11"/>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="14"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -9600,7 +9191,7 @@
       <c r="I160" s="5"/>
       <c r="J160" s="11"/>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="14"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -9612,7 +9203,7 @@
       <c r="I161" s="5"/>
       <c r="J161" s="11"/>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="14"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -9624,7 +9215,7 @@
       <c r="I162" s="5"/>
       <c r="J162" s="11"/>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="14"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -9636,7 +9227,7 @@
       <c r="I163" s="5"/>
       <c r="J163" s="11"/>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="14"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -9648,7 +9239,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="11"/>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="14"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -9660,7 +9251,7 @@
       <c r="I165" s="5"/>
       <c r="J165" s="11"/>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="14"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -9672,7 +9263,7 @@
       <c r="I166" s="5"/>
       <c r="J166" s="11"/>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="14"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -9684,7 +9275,7 @@
       <c r="I167" s="5"/>
       <c r="J167" s="11"/>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="14"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -9696,7 +9287,7 @@
       <c r="I168" s="5"/>
       <c r="J168" s="11"/>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="14"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -9708,7 +9299,7 @@
       <c r="I169" s="5"/>
       <c r="J169" s="11"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="14"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -9720,7 +9311,7 @@
       <c r="I170" s="5"/>
       <c r="J170" s="11"/>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="14"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -9732,7 +9323,7 @@
       <c r="I171" s="5"/>
       <c r="J171" s="11"/>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="14"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -9744,7 +9335,7 @@
       <c r="I172" s="5"/>
       <c r="J172" s="11"/>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="14"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -9756,7 +9347,7 @@
       <c r="I173" s="5"/>
       <c r="J173" s="11"/>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="14"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -9768,7 +9359,7 @@
       <c r="I174" s="5"/>
       <c r="J174" s="11"/>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="14"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -9780,7 +9371,7 @@
       <c r="I175" s="5"/>
       <c r="J175" s="11"/>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="14"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -9792,7 +9383,7 @@
       <c r="I176" s="5"/>
       <c r="J176" s="11"/>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="14"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -9804,7 +9395,7 @@
       <c r="I177" s="5"/>
       <c r="J177" s="11"/>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="14"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -9816,7 +9407,7 @@
       <c r="I178" s="5"/>
       <c r="J178" s="11"/>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="14"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -9828,7 +9419,7 @@
       <c r="I179" s="5"/>
       <c r="J179" s="11"/>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="14"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -9840,7 +9431,7 @@
       <c r="I180" s="5"/>
       <c r="J180" s="11"/>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="14"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -9852,7 +9443,7 @@
       <c r="I181" s="5"/>
       <c r="J181" s="11"/>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="14"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -9864,7 +9455,7 @@
       <c r="I182" s="5"/>
       <c r="J182" s="11"/>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="14"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -9876,7 +9467,7 @@
       <c r="I183" s="5"/>
       <c r="J183" s="11"/>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="14"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -9888,7 +9479,7 @@
       <c r="I184" s="5"/>
       <c r="J184" s="11"/>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="14"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -9900,7 +9491,7 @@
       <c r="I185" s="5"/>
       <c r="J185" s="11"/>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="14"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -9912,7 +9503,7 @@
       <c r="I186" s="5"/>
       <c r="J186" s="11"/>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="14"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -9924,7 +9515,7 @@
       <c r="I187" s="5"/>
       <c r="J187" s="11"/>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="14"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -9936,7 +9527,7 @@
       <c r="I188" s="5"/>
       <c r="J188" s="11"/>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="14"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -9948,7 +9539,7 @@
       <c r="I189" s="5"/>
       <c r="J189" s="11"/>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="14"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -9960,7 +9551,7 @@
       <c r="I190" s="5"/>
       <c r="J190" s="11"/>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="14"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -9972,7 +9563,7 @@
       <c r="I191" s="5"/>
       <c r="J191" s="11"/>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="14"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -9984,7 +9575,7 @@
       <c r="I192" s="5"/>
       <c r="J192" s="11"/>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="14"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -9996,7 +9587,7 @@
       <c r="I193" s="5"/>
       <c r="J193" s="11"/>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="14"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -10008,7 +9599,7 @@
       <c r="I194" s="5"/>
       <c r="J194" s="11"/>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="14"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -10020,7 +9611,7 @@
       <c r="I195" s="5"/>
       <c r="J195" s="11"/>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="14"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -10032,7 +9623,7 @@
       <c r="I196" s="5"/>
       <c r="J196" s="11"/>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="14"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -10044,7 +9635,7 @@
       <c r="I197" s="5"/>
       <c r="J197" s="11"/>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="14"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -10056,7 +9647,7 @@
       <c r="I198" s="5"/>
       <c r="J198" s="11"/>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="14"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -10068,7 +9659,7 @@
       <c r="I199" s="5"/>
       <c r="J199" s="11"/>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="15"/>
       <c r="B200" s="16"/>
       <c r="C200" s="16"/>
@@ -10082,43 +9673,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2 F2:AMJ3 B2:E11 H4:AMJ7 G8:AMJ11 F12:AMJ19">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 D1:J1">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:D13">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:E15">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F11">
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G7">
-    <cfRule type="expression" dxfId="1" priority="7">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:AMJ1 E20:AMJ21 A22:AMJ1048576">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="1">
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
